--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Build (Monthly)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Simulator" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Investor's Stake" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sponsorship" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Valuation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Investor's Stake" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -38,7 +39,7 @@
     <numFmt numFmtId="178" formatCode="0.0x"/>
     <numFmt numFmtId="179" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -242,6 +243,12 @@
       <color rgb="FF333333"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF335231"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -400,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -547,6 +554,37 @@
     <xf numFmtId="170" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="179" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="24" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -837,7 +875,7 @@
     <row r="7">
       <c r="B7" s="54" t="inlineStr">
         <is>
-          <t>This workbook reverse-engineers the headline valuations in the pitch (R53.3m today -&gt; R129.5m in 2029 -&gt; R690m exit; model shown in $ at FX 18.5).</t>
+          <t>This workbook reverse-engineers the headline valuations in the pitch (R53.3m today -&gt; R135.2m in 2029 -&gt; R744m exit; model shown in $ at FX 18.5).</t>
         </is>
       </c>
     </row>
@@ -899,7 +937,7 @@
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>THE FIVE TABS</t>
+          <t>THE SIX TABS</t>
         </is>
       </c>
     </row>
@@ -920,26 +958,30 @@
     <row r="20">
       <c r="B20" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. Valuation      — annual P&amp;L summary + the R53.3m / R129.5m / R690m bridge, base plan and simulator channel shown separately.</t>
+          <t xml:space="preserve">   3. Valuation      — annual P&amp;L summary + the R53.3m / R135.2m / R744m bridge, revenue reported by stream.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. Simulator      — simulator channel: unit economics, attach ramp and the 2029 sensitivity (incl. the 0% no-partnership case).</t>
+          <t xml:space="preserve">   4. Simulator      — simulator stream: unit economics, attach ramp and the 2029 adoption range.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. Investor's Stake — what 15% bought for R8m is worth at each milestone.</t>
+          <t xml:space="preserve">   5. Sponsorship    — the contracted Santam deal and the per-territory anchor partners that repeat it.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   6. Investor's Stake — what 15% bought for R8m is worth at each milestone.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="54" t="n"/>
@@ -1354,12 +1396,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>129733000/Assumptions!$C$11</f>
+        <f>135200000/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R129.5m, incl. simulator channel)</t>
+          <t>Pitch milestone — 3-yr plan (R135.2m, all revenue streams)</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1412,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>690000000/Assumptions!$C$11</f>
+        <f>744000000/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Pitch exit vision (R690m, incl. simulator channel)</t>
+          <t>Pitch exit vision (R744m, all revenue streams)</t>
         </is>
       </c>
     </row>
@@ -3025,17 +3067,17 @@
     <row r="6">
       <c r="B6" s="67" t="inlineStr">
         <is>
-          <t>Partnership status</t>
-        </is>
-      </c>
-      <c r="C6" s="68" t="inlineStr">
-        <is>
-          <t>NOT CONTRACTED</t>
+          <t>Stream status</t>
+        </is>
+      </c>
+      <c r="C6" s="100" t="inlineStr">
+        <is>
+          <t>LAUNCHING 2027</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
         <is>
-          <t>No agreement exists with Golfzon or any other operator, and there is no assurance one will be concluded.</t>
+          <t>Revenue stream 4 of 4. Integration funded by this round (20% of the R8m raise).</t>
         </is>
       </c>
     </row>
@@ -3070,6 +3112,23 @@
       <c r="E8" s="69" t="inlineStr">
         <is>
           <t>Ernie Els has direct relationships with the target operators and opens the door himself. Access, not a contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operator agreements</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>Not yet signed</t>
+        </is>
+      </c>
+      <c r="E9" s="101" t="inlineStr">
+        <is>
+          <t>No operator agreement is signed as at August 2026. Simulator revenue depends on concluding one.</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3552,7 @@
       </c>
       <c r="I33" s="69" t="inlineStr">
         <is>
-          <t>no partnership lands</t>
+          <t>no adoption — model floor</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3582,7 @@
       </c>
       <c r="I34" s="69" t="inlineStr">
         <is>
-          <t>slow adoption</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -3583,14 +3642,14 @@
       </c>
       <c r="I36" s="69" t="inlineStr">
         <is>
-          <t>strong adoption</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="69" t="inlineStr">
         <is>
-          <t>Investor multiple = company valuation at the 2029 milestone divided by the post-money valuation of this round. The 0% row is the base plan standing alone — the outcome if no operator agreement is ever concluded.</t>
+          <t>Investor multiple = company valuation at the 2029 milestone divided by the post-money valuation of this round. Attach rate is a live input — set it to zero to model the group without the simulator stream.</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3664,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t>TERRITORY SPONSORSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="65" t="inlineStr">
+        <is>
+          <t>Blue = change me.  Yellow = key assumption.  Black = calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>THE PROOF POINT</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="inlineStr"/>
+      <c r="D5" s="66" t="inlineStr"/>
+      <c r="E5" s="66" t="inlineStr"/>
+      <c r="F5" s="66" t="inlineStr"/>
+      <c r="G5" s="66" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E6" s="102" t="inlineStr">
+        <is>
+          <t>Sponsorship is the one line in the plan that was signed rather than forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="inlineStr">
+        <is>
+          <t>Santam (Authorised FSP 3416)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="inlineStr">
+        <is>
+          <t>CONTRACTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t>Deal value (ZAR)</t>
+        </is>
+      </c>
+      <c r="C9" s="82" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E9" s="102" t="inlineStr">
+        <is>
+          <t>R9m over three years, in a market of roughly 150,000 golfers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Year 1 / 2 / 3 (ZAR)</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>R2.5m  -&gt;  R3.0m  -&gt;  R3.5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t>Golfer market</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E11" s="102" t="inlineStr">
+        <is>
+          <t>The insurer who underwrites the prize is the natural sponsor of it — which is why the deal was signable in a small market and why it repeats in large ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="102" t="inlineStr">
+        <is>
+          <t>South African sponsorship already sits in the "Sponsorship revenue" row of the Valuation tab, off the monthly build. This tab models NEW territories only, so nothing is double-counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="66" t="inlineStr">
+        <is>
+          <t>NEW TERRITORIES</t>
+        </is>
+      </c>
+      <c r="C15" s="66" t="inlineStr"/>
+      <c r="D15" s="66" t="inlineStr"/>
+      <c r="E15" s="66" t="inlineStr"/>
+      <c r="F15" s="66" t="inlineStr"/>
+      <c r="G15" s="66" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="76" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="C16" s="76" t="inlineStr">
+        <is>
+          <t>Anchor partner</t>
+        </is>
+      </c>
+      <c r="D16" s="76" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="E16" s="76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F16" s="76" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="G16" s="76" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>Anchor insurer partner — appointed at market entry</t>
+        </is>
+      </c>
+      <c r="D17" s="103" t="n">
+        <v>2029</v>
+      </c>
+      <c r="E17" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="104" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G17" s="104" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I17" s="102" t="inlineStr">
+        <is>
+          <t>Live input — set each territory to what you believe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>Anchor insurer partner — appointed at market entry</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E18" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="104" t="n">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>Anchor insurer partner — appointed at market entry</t>
+        </is>
+      </c>
+      <c r="D19" s="103" t="n">
+        <v>2031</v>
+      </c>
+      <c r="E19" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="104" t="n">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>Total new-territory sponsorship (ZAR)</t>
+        </is>
+      </c>
+      <c r="E20" s="105">
+        <f>SUM(E17:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="105">
+        <f>SUM(F17:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="105">
+        <f>SUM(G17:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>Total new-territory sponsorship ($)</t>
+        </is>
+      </c>
+      <c r="E21" s="80">
+        <f>E20/Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="F21" s="80">
+        <f>F20/Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="G21" s="80">
+        <f>G20/Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="I21" s="102" t="inlineStr">
+        <is>
+          <t>This row feeds the Valuation tab (2026 = col E, 2029 = col F, 2032 = col G).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>EBITDA margin on sponsorship</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="102" t="inlineStr">
+        <is>
+          <t>After local activation and partner servicing cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="102" t="inlineStr">
+        <is>
+          <t>Every new-territory figure is set BELOW the South African run-rate at entry, in markets many times its size. Sponsorship is negotiated and lumpy: a linear scale off golfer counts would produce numbers no sponsor would sign. New-territory partners are appointed as each market opens and are not yet in place.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3672,7 +4058,7 @@
         <v/>
       </c>
       <c r="F6" s="86" t="n"/>
-      <c r="G6" s="69" t="inlineStr">
+      <c r="G6" s="102" t="inlineStr">
         <is>
           <t>2032 extends the Yr3 exit ramp</t>
         </is>
@@ -3697,7 +4083,7 @@
         <v/>
       </c>
       <c r="F7" s="86" t="n"/>
-      <c r="G7" s="69" t="inlineStr">
+      <c r="G7" s="102" t="inlineStr">
         <is>
           <t>Sum of MRR across months 1-12 (actual 2026 revenue)</t>
         </is>
@@ -3706,7 +4092,7 @@
     <row r="8">
       <c r="B8" s="67" t="inlineStr">
         <is>
-          <t>Sponsorship revenue ($)</t>
+          <t>Sponsorship revenue — South Africa ($)</t>
         </is>
       </c>
       <c r="C8" s="88">
@@ -3722,16 +4108,16 @@
         <v/>
       </c>
       <c r="F8" s="86" t="n"/>
-      <c r="G8" s="69" t="inlineStr">
-        <is>
-          <t>Sum of monthly sponsorship across 2026</t>
+      <c r="G8" s="102" t="inlineStr">
+        <is>
+          <t>The contracted Santam deal, off the monthly build</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>Base plan revenue ($)</t>
+          <t>Courses &amp; app subscription ($)</t>
         </is>
       </c>
       <c r="C9" s="89">
@@ -3747,16 +4133,16 @@
         <v/>
       </c>
       <c r="F9" s="86" t="n"/>
-      <c r="G9" s="69" t="inlineStr">
-        <is>
-          <t>Subscriptions + sponsorship. This is the plan an investor can underwrite WITHOUT any simulator partnership.</t>
+      <c r="G9" s="102" t="inlineStr">
+        <is>
+          <t>Installed courses, membership and the global app subscription, plus contracted South African sponsorship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="67" t="inlineStr">
         <is>
-          <t>Simulator channel revenue ($)</t>
+          <t>Simulator revenue ($)</t>
         </is>
       </c>
       <c r="C10" s="90">
@@ -3772,128 +4158,124 @@
         <v/>
       </c>
       <c r="F10" s="86" t="n"/>
-      <c r="G10" s="69" t="inlineStr">
-        <is>
-          <t>From the Simulator tab. NOT CONTRACTED — modelled at 1.5% of South Korea simulator rounds by 2029.</t>
+      <c r="G10" s="102" t="inlineStr">
+        <is>
+          <t>From the Simulator tab. Revenue stream 4, live from 2027; integration funded by this round.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="B11" s="75" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t>Territory sponsorship ($)</t>
+        </is>
+      </c>
+      <c r="C11" s="90">
+        <f>Sponsorship!E21</f>
+        <v/>
+      </c>
+      <c r="D11" s="90">
+        <f>Sponsorship!F21</f>
+        <v/>
+      </c>
+      <c r="E11" s="90">
+        <f>Sponsorship!G21</f>
+        <v/>
+      </c>
+      <c r="F11" s="86" t="n"/>
+      <c r="G11" s="102" t="inlineStr">
+        <is>
+          <t>From the Sponsorship tab. The signed Santam deal repeated with an anchor insurer partner per new market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Total annual revenue ($)</t>
         </is>
       </c>
-      <c r="C11" s="89">
-        <f>C9+C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="89">
-        <f>D9+D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="89">
-        <f>E9+E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="86" t="n"/>
-      <c r="G11" s="69" t="inlineStr">
-        <is>
-          <t>Base plan + simulator channel. Drives the valuation walk below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>Gross profit — base plan ($)</t>
-        </is>
-      </c>
-      <c r="C12" s="79">
-        <f>C9*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="D12" s="79">
-        <f>D9*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="E12" s="79">
-        <f>E9*Assumptions!$C$22</f>
+      <c r="C12" s="80">
+        <f>C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="80">
+        <f>D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="80">
+        <f>E9+E10+E11</f>
         <v/>
       </c>
       <c r="F12" s="86" t="n"/>
-      <c r="G12" s="69" t="inlineStr">
-        <is>
-          <t>Base plan revenue at the stated gross margin.</t>
+      <c r="G12" s="102" t="inlineStr">
+        <is>
+          <t>Drives the valuation walk below.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="B13" s="91" t="inlineStr">
         <is>
-          <t>EBITDA proxy — base plan ($)</t>
+          <t>Gross profit — courses &amp; app ($)</t>
         </is>
       </c>
       <c r="C13" s="79">
-        <f>C12-Assumptions!$C$26*12*(C6/$C$6)^Assumptions!$C$27-C9*Assumptions!$C$24</f>
+        <f>C9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="D13" s="79">
-        <f>D12-Assumptions!$C$26*12*(D6/$C$6)^Assumptions!$C$27-D9*Assumptions!$C$24</f>
+        <f>D9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="E13" s="79">
-        <f>E12-Assumptions!$C$26*12*(E6/$C$6)^Assumptions!$C$27-E9*Assumptions!$C$24</f>
+        <f>E9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="F13" s="86" t="n"/>
-      <c r="G13" s="69" t="inlineStr">
-        <is>
-          <t>GP less scaled opex less insurance premium (24% of revenue, 100% cover). Prize payouts excluded — carried by the insurer.</t>
-        </is>
-      </c>
+      <c r="G13" s="106" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="67" t="inlineStr">
         <is>
-          <t>EBITDA proxy — simulator channel ($)</t>
+          <t>EBITDA proxy — courses &amp; app ($)</t>
         </is>
       </c>
       <c r="C14" s="88">
+        <f>C13-Assumptions!$C$26*12*(C6/$C$6)^Assumptions!$C$27-C9*Assumptions!$C$24</f>
+        <v/>
+      </c>
+      <c r="D14" s="88">
+        <f>D13-Assumptions!$C$26*12*(D6/$C$6)^Assumptions!$C$27-D9*Assumptions!$C$24</f>
+        <v/>
+      </c>
+      <c r="E14" s="88">
+        <f>E13-Assumptions!$C$26*12*(E6/$C$6)^Assumptions!$C$27-E9*Assumptions!$C$24</f>
+        <v/>
+      </c>
+      <c r="F14" s="86" t="n"/>
+      <c r="G14" s="102" t="inlineStr">
+        <is>
+          <t>GP less scaled opex less insurance premium. Prize payouts excluded — carried by the insurer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>EBITDA proxy — simulators ($)</t>
+        </is>
+      </c>
+      <c r="C15" s="88">
         <f>C10*Simulator!$C$17</f>
         <v/>
       </c>
-      <c r="D14" s="88">
+      <c r="D15" s="88">
         <f>D10*Simulator!$C$17</f>
         <v/>
       </c>
-      <c r="E14" s="88">
+      <c r="E15" s="88">
         <f>E10*Simulator!$C$17</f>
-        <v/>
-      </c>
-      <c r="F14" s="86" t="n"/>
-      <c r="G14" s="69" t="inlineStr">
-        <is>
-          <t>Software-only channel at the margin set on the Simulator tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="75" t="inlineStr">
-        <is>
-          <t>EBITDA proxy — total ($)</t>
-        </is>
-      </c>
-      <c r="C15" s="89">
-        <f>C13+C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="89">
-        <f>D13+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="89">
-        <f>E13+E14</f>
         <v/>
       </c>
       <c r="F15" s="86" t="n"/>
@@ -3902,279 +4284,361 @@
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="67" t="inlineStr">
         <is>
-          <t>EBITDA margin (% of total revenue)</t>
-        </is>
-      </c>
-      <c r="C16" s="93">
-        <f>IFERROR(C15/C11,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="93">
-        <f>IFERROR(D15/D11,0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="93">
-        <f>IFERROR(E15/E11,0)</f>
+          <t>EBITDA proxy — territory sponsorship ($)</t>
+        </is>
+      </c>
+      <c r="C16" s="88">
+        <f>C11*Sponsorship!$C$22</f>
+        <v/>
+      </c>
+      <c r="D16" s="88">
+        <f>D11*Sponsorship!$C$22</f>
+        <v/>
+      </c>
+      <c r="E16" s="88">
+        <f>E11*Sponsorship!$C$22</f>
         <v/>
       </c>
       <c r="F16" s="86" t="n"/>
       <c r="G16" s="92" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="86" t="n"/>
-      <c r="C17" s="94" t="n"/>
-      <c r="D17" s="94" t="n"/>
-      <c r="E17" s="94" t="n"/>
+      <c r="B17" s="75" t="inlineStr">
+        <is>
+          <t>EBITDA proxy — total ($)</t>
+        </is>
+      </c>
+      <c r="C17" s="80">
+        <f>C14+C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="80">
+        <f>D14+D15+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="80">
+        <f>E14+E15+E16</f>
+        <v/>
+      </c>
       <c r="F17" s="86" t="n"/>
       <c r="G17" s="92" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B18" s="107" t="inlineStr">
+        <is>
+          <t>EBITDA margin (% of total revenue)</t>
+        </is>
+      </c>
+      <c r="C18" s="108">
+        <f>IFERROR(C17/C12,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="108">
+        <f>IFERROR(D17/D12,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="108">
+        <f>IFERROR(E17/E12,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="95" t="n"/>
+      <c r="G18" s="95" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="109" t="n"/>
+      <c r="D19" s="109" t="n"/>
+      <c r="E19" s="109" t="n"/>
+      <c r="F19" s="86" t="n"/>
+      <c r="G19" s="106" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>VALUATION WALK</t>
         </is>
       </c>
-      <c r="C18" s="66" t="inlineStr"/>
-      <c r="D18" s="66" t="inlineStr"/>
-      <c r="E18" s="66" t="inlineStr"/>
-      <c r="F18" s="66" t="inlineStr"/>
-      <c r="G18" s="66" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="67" t="inlineStr">
-        <is>
-          <t>Implied revenue multiple</t>
-        </is>
-      </c>
-      <c r="C19" s="99">
-        <f>Assumptions!$C$8/C11</f>
-        <v/>
-      </c>
-      <c r="D19" s="99">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="E19" s="99">
-        <f>Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="F19" s="86" t="n"/>
-      <c r="G19" s="69" t="inlineStr">
-        <is>
-          <t>Today solved to the post-money floor; out-years from Assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="67" t="inlineStr">
-        <is>
-          <t>Valuation milestone — pitch ($)</t>
-        </is>
-      </c>
-      <c r="C20" s="79">
-        <f>Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="D20" s="79">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E20" s="79">
-        <f>Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="F20" s="86" t="n"/>
-      <c r="G20" s="69" t="inlineStr">
-        <is>
-          <t>Headline figures from the pitch: R53.3m / R129.5m / R690m.</t>
-        </is>
-      </c>
+      <c r="C20" s="110" t="inlineStr"/>
+      <c r="D20" s="110" t="inlineStr"/>
+      <c r="E20" s="110" t="inlineStr"/>
+      <c r="F20" s="66" t="inlineStr"/>
+      <c r="G20" s="66" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="67" t="inlineStr">
         <is>
-          <t>Valuation — model-implied ($)</t>
-        </is>
-      </c>
-      <c r="C21" s="79">
-        <f>C11*C19</f>
-        <v/>
-      </c>
-      <c r="D21" s="79">
-        <f>D11*D19</f>
-        <v/>
-      </c>
-      <c r="E21" s="79">
-        <f>E11*E19</f>
+          <t>Implied revenue multiple</t>
+        </is>
+      </c>
+      <c r="C21" s="83">
+        <f>Assumptions!$C$8/C12</f>
+        <v/>
+      </c>
+      <c r="D21" s="83">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="E21" s="83">
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="F21" s="86" t="n"/>
-      <c r="G21" s="69" t="inlineStr">
-        <is>
-          <t>Sanity check: does the ramp x multiple reach the milestone?</t>
+      <c r="G21" s="102" t="inlineStr">
+        <is>
+          <t>Today solved to the post-money floor; out-years from Assumptions.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="95" t="n"/>
-      <c r="C22" s="86" t="n"/>
-      <c r="D22" s="86" t="n"/>
-      <c r="E22" s="86" t="n"/>
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>Valuation milestone — pitch ($)</t>
+        </is>
+      </c>
+      <c r="C22" s="79">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="D22" s="79">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E22" s="79">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
       <c r="F22" s="86" t="n"/>
-      <c r="G22" s="86" t="n"/>
+      <c r="G22" s="102" t="inlineStr">
+        <is>
+          <t>Headline figures from the pitch: R53.3m / R135.2m / R744m.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="13" customFormat="1" customHeight="1" s="35">
       <c r="B23" s="67" t="inlineStr">
         <is>
-          <t>Memo — model valuation in ZAR</t>
-        </is>
-      </c>
-      <c r="C23" s="81">
-        <f>C21*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="D23" s="81">
-        <f>D21*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="E23" s="81">
-        <f>E21*Assumptions!$C$11</f>
+          <t>Valuation — model-implied ($)</t>
+        </is>
+      </c>
+      <c r="C23" s="79">
+        <f>C12*C21</f>
+        <v/>
+      </c>
+      <c r="D23" s="79">
+        <f>D12*D21</f>
+        <v/>
+      </c>
+      <c r="E23" s="79">
+        <f>E12*E21</f>
         <v/>
       </c>
       <c r="F23" s="86" t="n"/>
-      <c r="G23" s="86" t="n"/>
+      <c r="G23" s="102" t="inlineStr">
+        <is>
+          <t>Sanity check: does the ramp x multiple reach the milestone?</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="13" customFormat="1" customHeight="1" s="35">
-      <c r="B24" s="67" t="inlineStr">
-        <is>
-          <t>Memo — pitch milestone in ZAR</t>
-        </is>
-      </c>
-      <c r="C24" s="81">
-        <f>C20*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="D24" s="81">
-        <f>D20*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="E24" s="81">
-        <f>E20*Assumptions!$C$11</f>
-        <v/>
-      </c>
+      <c r="B24" s="86" t="n"/>
+      <c r="C24" s="111" t="n"/>
+      <c r="D24" s="111" t="n"/>
+      <c r="E24" s="111" t="n"/>
       <c r="F24" s="86" t="n"/>
       <c r="G24" s="86" t="n"/>
     </row>
     <row r="25" ht="13" customFormat="1" customHeight="1" s="35">
       <c r="B25" s="67" t="inlineStr">
         <is>
-          <t>Memo — base plan only, no simulator (ZAR)</t>
+          <t>Memo — model valuation in ZAR</t>
         </is>
       </c>
       <c r="C25" s="81">
-        <f>C9*C19*Assumptions!$C$11</f>
+        <f>C23*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D25" s="81">
-        <f>D9*D19*Assumptions!$C$11</f>
+        <f>D23*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>E9*E19*Assumptions!$C$11</f>
+        <f>E23*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="F25" s="86" t="n"/>
-      <c r="G25" s="69" t="inlineStr">
-        <is>
-          <t>The downside case published in the dataroom: if no operator agreement lands, this is where the milestone sits.</t>
-        </is>
-      </c>
+      <c r="G25" s="106" t="n"/>
     </row>
     <row r="26" ht="14" customFormat="1" customHeight="1" s="46">
-      <c r="B26" s="86" t="n"/>
-      <c r="C26" s="86" t="n"/>
-      <c r="D26" s="86" t="n"/>
-      <c r="E26" s="86" t="n"/>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>Memo — pitch milestone in ZAR</t>
+        </is>
+      </c>
+      <c r="C26" s="81">
+        <f>C22*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="D26" s="81">
+        <f>D22*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="E26" s="81">
+        <f>E22*Assumptions!$C$11</f>
+        <v/>
+      </c>
       <c r="F26" s="86" t="n"/>
       <c r="G26" s="86" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="66" t="inlineStr">
-        <is>
-          <t>WHY 6x REVENUE AT EXIT (2032)</t>
-        </is>
-      </c>
-      <c r="C27" s="66" t="inlineStr"/>
-      <c r="D27" s="66" t="inlineStr"/>
-      <c r="E27" s="66" t="inlineStr"/>
-      <c r="F27" s="66" t="inlineStr"/>
-      <c r="G27" s="66" t="inlineStr"/>
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>Memo — revenue by stream in ZAR</t>
+        </is>
+      </c>
+      <c r="C27" s="112">
+        <f>C12*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="D27" s="112">
+        <f>D12*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="E27" s="112">
+        <f>E12*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="F27" s="95" t="n"/>
+      <c r="G27" s="102" t="inlineStr">
+        <is>
+          <t>Total revenue in rand. Stream split is rows 9-11 above.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="67" t="inlineStr">
-        <is>
-          <t>Engaged subscriber database</t>
-        </is>
-      </c>
-      <c r="C28" s="96" t="inlineStr">
-        <is>
-          <t>Recurring golfers opted into a high-intent niche product are the core asset — a clean, targetable distribution channel for golf brands, media partners and sponsors. The valuation reflects the database itself, not just the topline.</t>
-        </is>
-      </c>
+      <c r="B28" s="86" t="n"/>
+      <c r="C28" s="113" t="n"/>
       <c r="D28" s="86" t="n"/>
       <c r="E28" s="86" t="n"/>
       <c r="F28" s="86" t="n"/>
       <c r="G28" s="86" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="67" t="inlineStr">
-        <is>
-          <t>Strategic partner optionality</t>
-        </is>
-      </c>
-      <c r="C29" s="96" t="inlineStr">
-        <is>
-          <t>At scale, the platform unlocks multiple exit paths: license access to a golf brand (Callaway/TaylorMade), co-brand prize pools with a tour or media rights holder, integrate with a sportsbook, or sell outright to a sports-tech acquirer. Optionality justifies a strategic premium over pure SaaS multiples.</t>
-        </is>
-      </c>
-      <c r="D29" s="86" t="n"/>
-      <c r="E29" s="86" t="n"/>
-      <c r="F29" s="86" t="n"/>
-      <c r="G29" s="86" t="n"/>
+      <c r="B29" s="66" t="inlineStr">
+        <is>
+          <t>WHY 6x REVENUE AT EXIT (2032)</t>
+        </is>
+      </c>
+      <c r="C29" s="66" t="inlineStr"/>
+      <c r="D29" s="66" t="inlineStr"/>
+      <c r="E29" s="66" t="inlineStr"/>
+      <c r="F29" s="66" t="inlineStr"/>
+      <c r="G29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="67" t="inlineStr">
         <is>
-          <t>Comparable engaged communities</t>
-        </is>
-      </c>
-      <c r="C30" s="96" t="inlineStr">
-        <is>
-          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) have transacted in the 5-10x revenue range at similar scale. 6x sits mid-band — conservative for a niche category leader with strategic upside.</t>
-        </is>
-      </c>
+          <t>Engaged subscriber database</t>
+        </is>
+      </c>
+      <c r="C30" s="114" t="inlineStr">
+        <is>
+          <t>Recurring golfers opted into a high-intent niche product are the core asset — a clean, targetable distribution channel for golf brands, media partners and sponsors. The valuation reflects the database itself, not just the topline.</t>
+        </is>
+      </c>
+      <c r="D30" s="86" t="n"/>
+      <c r="E30" s="86" t="n"/>
+      <c r="F30" s="86" t="n"/>
+      <c r="G30" s="86" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="67" t="inlineStr">
         <is>
-          <t>Risk to the multiple</t>
-        </is>
-      </c>
-      <c r="C31" s="96" t="inlineStr">
-        <is>
-          <t>If sub growth stalls or the engaged-community thesis weakens, the multiple compresses toward pure SaaS (3-4x), which would land 2032 closer to R345-460m rather than R690m.</t>
-        </is>
-      </c>
+          <t>Four revenue streams, one product</t>
+        </is>
+      </c>
+      <c r="C31" s="114" t="inlineStr">
+        <is>
+          <t>Installed courses, membership, the global app subscription and simulators sell the same insured challenge through four channels, with sponsorship attached to each territory. Diversified revenue on one cost base.</t>
+        </is>
+      </c>
+      <c r="D31" s="86" t="n"/>
+      <c r="E31" s="86" t="n"/>
+      <c r="F31" s="86" t="n"/>
+      <c r="G31" s="86" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="67" t="inlineStr">
         <is>
-          <t>Risk to the simulator channel</t>
-        </is>
-      </c>
-      <c r="C32" s="96" t="inlineStr">
-        <is>
-          <t>The simulator line is modelled, not contracted. If no operator agreement is concluded the 2029 milestone falls to the base plan alone — see the sensitivity table on the Simulator tab, and the "base plan only" memo above.</t>
+          <t>Strategic partner optionality</t>
+        </is>
+      </c>
+      <c r="C32" s="114" t="inlineStr">
+        <is>
+          <t>At scale the platform unlocks multiple exit paths: license access to a golf brand, co-brand prize pools with a tour or media rights holder, integrate with a sportsbook, or sell outright to a sports-tech acquirer.</t>
+        </is>
+      </c>
+      <c r="D32" s="86" t="n"/>
+      <c r="E32" s="86" t="n"/>
+      <c r="F32" s="86" t="n"/>
+      <c r="G32" s="86" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="67" t="inlineStr">
+        <is>
+          <t>Comparable engaged communities</t>
+        </is>
+      </c>
+      <c r="C33" s="114" t="inlineStr">
+        <is>
+          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) have transacted in the 5-10x revenue range at similar scale. 6x sits mid-band.</t>
+        </is>
+      </c>
+      <c r="D33" s="86" t="n"/>
+      <c r="E33" s="86" t="n"/>
+      <c r="F33" s="86" t="n"/>
+      <c r="G33" s="86" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="67" t="inlineStr">
+        <is>
+          <t>Risk to the multiple</t>
+        </is>
+      </c>
+      <c r="C34" s="114" t="inlineStr">
+        <is>
+          <t>If growth stalls the multiple compresses toward pure SaaS (3-4x), landing 2032 at R372-496m rather than R744m.</t>
+        </is>
+      </c>
+      <c r="D34" s="86" t="n"/>
+      <c r="E34" s="86" t="n"/>
+      <c r="F34" s="86" t="n"/>
+      <c r="G34" s="86" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>Risk to the simulator stream</t>
+        </is>
+      </c>
+      <c r="C35" s="114" t="inlineStr">
+        <is>
+          <t>Simulator revenue depends on concluding operator agreements, which are not yet signed as at August 2026. Ernie Els holds direct relationships with the target operators; the integration this round funds is what makes Get Lucky ready to sign. Set the attach rate to zero on the Simulator tab to model the group without the stream.</t>
+        </is>
+      </c>
+      <c r="D35" s="86" t="n"/>
+      <c r="E35" s="86" t="n"/>
+      <c r="F35" s="86" t="n"/>
+      <c r="G35" s="86" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Risk to territory sponsorship</t>
+        </is>
+      </c>
+      <c r="C36" s="114" t="inlineStr">
+        <is>
+          <t>South African sponsorship is contracted. New-territory anchor partners are appointed as each market opens and are not yet in place. Per-territory figures are live inputs on the Sponsorship tab.</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4242,15 +4706,15 @@
         </is>
       </c>
       <c r="C6" s="44">
-        <f>Valuation!C20</f>
+        <f>Valuation!C22</f>
         <v/>
       </c>
       <c r="D6" s="44">
-        <f>Valuation!D20</f>
+        <f>Valuation!D22</f>
         <v/>
       </c>
       <c r="E6" s="44">
-        <f>Valuation!E20</f>
+        <f>Valuation!E22</f>
         <v/>
       </c>
       <c r="F6" s="20" t="inlineStr">

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Build (Monthly)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Simulator" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sponsorship" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Valuation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Investor's Stake" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Upsells" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Investor's Stake" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -407,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -581,6 +582,34 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="173" fontId="27" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -875,7 +904,7 @@
     <row r="7">
       <c r="B7" s="54" t="inlineStr">
         <is>
-          <t>This workbook reverse-engineers the headline valuations in the pitch (R53.3m today -&gt; R135.2m in 2029 -&gt; R744m exit; model shown in $ at FX 18.5).</t>
+          <t>This workbook reverse-engineers the headline valuations in the pitch (R53.3m today -&gt; R147m in 2029 -&gt; R807m exit; model shown in $ at FX 18.5).</t>
         </is>
       </c>
     </row>
@@ -937,7 +966,7 @@
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>THE SIX TABS</t>
+          <t>THE SEVEN TABS</t>
         </is>
       </c>
     </row>
@@ -958,7 +987,7 @@
     <row r="20">
       <c r="B20" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. Valuation      — annual P&amp;L summary + the R53.3m / R135.2m / R744m bridge, revenue reported by stream.</t>
+          <t xml:space="preserve">   3. Valuation      — annual P&amp;L summary + the R53.3m / R147m / R807m bridge, revenue reported by stream.</t>
         </is>
       </c>
     </row>
@@ -979,12 +1008,16 @@
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6. Investor's Stake — what 15% bought for R8m is worth at each milestone.</t>
+          <t xml:space="preserve">   6. Upsells        — the in-play menu, attach rates and the revenue it adds to attempts already modelled.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="54" t="n"/>
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   7. Investor's Stake — what 15% bought for R8m is worth at each milestone.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="54" t="n"/>
@@ -1396,12 +1429,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>135200000/Assumptions!$C$11</f>
+        <f>147000000/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R135.2m, all revenue streams)</t>
+          <t>Pitch milestone — 3-yr plan (R147m, all revenue streams)</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1445,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>744000000/Assumptions!$C$11</f>
+        <f>807000000/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Pitch exit vision (R744m, all revenue streams)</t>
+          <t>Pitch exit vision (R807m, all revenue streams)</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3108,7 @@
           <t>LAUNCHING 2027</t>
         </is>
       </c>
-      <c r="E6" s="69" t="inlineStr">
+      <c r="E6" s="115" t="inlineStr">
         <is>
           <t>Revenue stream 4 of 4. Integration funded by this round (20% of the R8m raise).</t>
         </is>
@@ -3092,7 +3125,7 @@
           <t>Golfzon</t>
         </is>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>6,500+ venues, ~60% of the global commercial simulator market (Forbes / Seoulz).</t>
         </is>
@@ -3109,7 +3142,7 @@
           <t>Ernie Els — direct relationships</t>
         </is>
       </c>
-      <c r="E8" s="69" t="inlineStr">
+      <c r="E8" s="115" t="inlineStr">
         <is>
           <t>Ernie Els has direct relationships with the target operators and opens the door himself. Access, not a contract.</t>
         </is>
@@ -3150,7 +3183,7 @@
       <c r="C11" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="69" t="inlineStr">
+      <c r="E11" s="115" t="inlineStr">
         <is>
           <t>Price per in-sim challenge, charged inside the operator software.</t>
         </is>
@@ -3165,7 +3198,7 @@
       <c r="C12" s="70" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="69" t="inlineStr">
+      <c r="E12" s="115" t="inlineStr">
         <is>
           <t>Paid by the insurer on a verified ace. Get Lucky carries no prize risk.</t>
         </is>
@@ -3180,7 +3213,7 @@
       <c r="C13" s="71" t="n">
         <v>0.46</v>
       </c>
-      <c r="E13" s="69" t="inlineStr">
+      <c r="E13" s="115" t="inlineStr">
         <is>
           <t>Residual after operator and insurer shares. Key commercial assumption — confirm on signature.</t>
         </is>
@@ -3195,7 +3228,7 @@
       <c r="C14" s="71" t="n">
         <v>0.3</v>
       </c>
-      <c r="E14" s="69" t="inlineStr">
+      <c r="E14" s="115" t="inlineStr">
         <is>
           <t>More than a course 10%: the operator brings venues, software surface and distribution; Get Lucky installs no hardware.</t>
         </is>
@@ -3210,7 +3243,7 @@
       <c r="C15" s="72" t="n">
         <v>0.24</v>
       </c>
-      <c r="E15" s="69" t="inlineStr">
+      <c r="E15" s="115" t="inlineStr">
         <is>
           <t>Held identical to the on-course insurance premium assumption.</t>
         </is>
@@ -3226,7 +3259,7 @@
         <f>C13+C14+C15</f>
         <v/>
       </c>
-      <c r="E16" s="69" t="inlineStr">
+      <c r="E16" s="115" t="inlineStr">
         <is>
           <t>Must read 100.0%.</t>
         </is>
@@ -3241,7 +3274,7 @@
       <c r="C17" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="E17" s="69" t="inlineStr">
+      <c r="E17" s="115" t="inlineStr">
         <is>
           <t>Software-only channel: no cameras, no installation, no course revenue share. After integration engineering, operator marketing support and platform ops.</t>
         </is>
@@ -3265,7 +3298,7 @@
       <c r="C20" s="74" t="n">
         <v>94000000</v>
       </c>
-      <c r="E20" s="69" t="inlineStr">
+      <c r="E20" s="115" t="inlineStr">
         <is>
           <t>Source: GOLF.com — ~94M rounds logged on Golfzon simulators in South Korea in a single year. Korea ONLY: Golfzon venues elsewhere and all other operators are excluded from this model.</t>
         </is>
@@ -3336,7 +3369,7 @@
       <c r="G24" s="77" t="n">
         <v>0.04</v>
       </c>
-      <c r="I24" s="69" t="inlineStr">
+      <c r="I24" s="115" t="inlineStr">
         <is>
           <t>2026 is an integration year — no revenue modelled.</t>
         </is>
@@ -3422,7 +3455,7 @@
         <f>G26*$C$13</f>
         <v/>
       </c>
-      <c r="I27" s="69" t="inlineStr">
+      <c r="I27" s="115" t="inlineStr">
         <is>
           <t>This row feeds the Valuation tab (2026 = col C, 2029 = col F, 2032 = col G).</t>
         </is>
@@ -3550,7 +3583,7 @@
         <f>E33/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I33" s="69" t="inlineStr">
+      <c r="I33" s="115" t="inlineStr">
         <is>
           <t>no adoption — model floor</t>
         </is>
@@ -3580,7 +3613,7 @@
         <f>E34/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I34" s="69" t="inlineStr">
+      <c r="I34" s="115" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -3610,7 +3643,7 @@
         <f>E35/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I35" s="69" t="inlineStr">
+      <c r="I35" s="115" t="inlineStr">
         <is>
           <t>the plan</t>
         </is>
@@ -3640,14 +3673,14 @@
         <f>E36/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I36" s="69" t="inlineStr">
+      <c r="I36" s="115" t="inlineStr">
         <is>
           <t>strong</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="69" t="inlineStr">
+      <c r="B38" s="115" t="inlineStr">
         <is>
           <t>Investor multiple = company valuation at the 2029 milestone divided by the post-money valuation of this round. Attach rate is a live input — set it to zero to model the group without the simulator stream.</t>
         </is>
@@ -3715,7 +3748,7 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E6" s="102" t="inlineStr">
+      <c r="E6" s="115" t="inlineStr">
         <is>
           <t>Sponsorship is the one line in the plan that was signed rather than forecast.</t>
         </is>
@@ -3754,7 +3787,7 @@
       <c r="C9" s="82" t="n">
         <v>9000000</v>
       </c>
-      <c r="E9" s="102" t="inlineStr">
+      <c r="E9" s="115" t="inlineStr">
         <is>
           <t>R9m over three years, in a market of roughly 150,000 golfers.</t>
         </is>
@@ -3781,14 +3814,14 @@
       <c r="C11" s="78" t="n">
         <v>150000</v>
       </c>
-      <c r="E11" s="102" t="inlineStr">
+      <c r="E11" s="115" t="inlineStr">
         <is>
           <t>The insurer who underwrites the prize is the natural sponsor of it — which is why the deal was signable in a small market and why it repeats in large ones.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="102" t="inlineStr">
+      <c r="B13" s="115" t="inlineStr">
         <is>
           <t>South African sponsorship already sits in the "Sponsorship revenue" row of the Valuation tab, off the monthly build. This tab models NEW territories only, so nothing is double-counted.</t>
         </is>
@@ -3861,7 +3894,7 @@
       <c r="G17" s="104" t="n">
         <v>4000000</v>
       </c>
-      <c r="I17" s="102" t="inlineStr">
+      <c r="I17" s="115" t="inlineStr">
         <is>
           <t>Live input — set each territory to what you believe.</t>
         </is>
@@ -3952,7 +3985,7 @@
         <f>G20/Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="I21" s="102" t="inlineStr">
+      <c r="I21" s="115" t="inlineStr">
         <is>
           <t>This row feeds the Valuation tab (2026 = col E, 2029 = col F, 2032 = col G).</t>
         </is>
@@ -3967,14 +4000,14 @@
       <c r="C22" s="71" t="n">
         <v>0.6</v>
       </c>
-      <c r="E22" s="102" t="inlineStr">
+      <c r="E22" s="115" t="inlineStr">
         <is>
           <t>After local activation and partner servicing cost.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="102" t="inlineStr">
+      <c r="B24" s="115" t="inlineStr">
         <is>
           <t>Every new-territory figure is set BELOW the South African run-rate at entry, in markets many times its size. Sponsorship is negotiated and lumpy: a linear scale off golfer counts would produce numbers no sponsor would sign. New-territory partners are appointed as each market opens and are not yet in place.</t>
         </is>
@@ -3991,7 +4024,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G36"/>
+  <dimension ref="B2:I30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t>IN-PLAY UPSELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="65" t="inlineStr">
+        <is>
+          <t>Blue = change me.  Yellow = key assumption.  Black = calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="115" t="inlineStr">
+        <is>
+          <t>Sold AFTER the entry, when the golfer has already paid and is standing over the ball. Upsells attach to attempts already in the model — they never create new volume, so there is no double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>THE MENU</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr"/>
+      <c r="D6" s="66" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="76" t="inlineStr">
+        <is>
+          <t>Upsell</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D7" s="76" t="inlineStr">
+        <is>
+          <t>Insured</t>
+        </is>
+      </c>
+      <c r="E7" s="76" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="67" t="inlineStr">
+        <is>
+          <t>Jackpot upgrade</t>
+        </is>
+      </c>
+      <c r="C8" s="67" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" s="123" t="inlineStr">
+        <is>
+          <t>Trade up mid-round to a shot at a $100,000 insured prize instead of the standard pot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="67" t="inlineStr">
+        <is>
+          <t>Double up</t>
+        </is>
+      </c>
+      <c r="C9" s="67" t="inlineStr">
+        <is>
+          <t>$5</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="inlineStr">
+        <is>
+          <t>Doubles the prize if the shot goes in. Cheapest yes on the menu, highest attach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Three for two</t>
+        </is>
+      </c>
+      <c r="C10" s="67" t="inlineStr">
+        <is>
+          <t>2x entry</t>
+        </is>
+      </c>
+      <c r="D10" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="inlineStr">
+        <is>
+          <t>Three swings for the price of two. More attempts per visit, same prize exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="67" t="inlineStr">
+        <is>
+          <t>Nearest the pin</t>
+        </is>
+      </c>
+      <c r="C11" s="67" t="inlineStr">
+        <is>
+          <t>$3</t>
+        </is>
+      </c>
+      <c r="D11" s="67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="inlineStr">
+        <is>
+          <t>Guaranteed prize inside three feet — monetises the 12,499 shots in 12,500 that are not an ace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>The highlight reel</t>
+        </is>
+      </c>
+      <c r="C12" s="67" t="inlineStr">
+        <is>
+          <t>$3</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="inlineStr">
+        <is>
+          <t>The produced clip, scored and branded. No insurance component: pure margin, and every share is marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>The group pot</t>
+        </is>
+      </c>
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>$10 a head</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="inlineStr">
+        <is>
+          <t>A fourball buys in, closest to the pin takes the pot, Get Lucky takes a fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="66" t="inlineStr">
+        <is>
+          <t>ATTACH ASSUMPTIONS</t>
+        </is>
+      </c>
+      <c r="C15" s="66" t="inlineStr"/>
+      <c r="D15" s="66" t="inlineStr"/>
+      <c r="E15" s="66" t="inlineStr"/>
+      <c r="F15" s="66" t="inlineStr"/>
+      <c r="G15" s="66" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="67" t="inlineStr">
+        <is>
+          <t>Course &amp; app — attach rate</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I16" s="115" t="inlineStr">
+        <is>
+          <t>Share of subscriber rounds that buy at least one upsell. This golfer already pays ~R200 a swing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>Course &amp; app — average spend ($)</t>
+        </is>
+      </c>
+      <c r="C17" s="116" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="115" t="inlineStr">
+        <is>
+          <t>Blend across the menu on an attaching entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>Simulator — attach rate</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" s="115" t="inlineStr">
+        <is>
+          <t>Lower: the base simulator entry is $1, so the ask has to be smaller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>Simulator — average spend ($)</t>
+        </is>
+      </c>
+      <c r="C19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="115" t="inlineStr">
+        <is>
+          <t>Blend across the menu inside a simulator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t>Get Lucky net share</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I20" s="115" t="inlineStr">
+        <is>
+          <t>After course or operator share and insurance. Higher than the 46% simulator entry share because part of the menu (highlight reel, group pot) carries no insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I21" s="115" t="inlineStr">
+        <is>
+          <t>Sold through the existing checkout: no hardware, no new venue cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Rounds per subscriber per month</t>
+        </is>
+      </c>
+      <c r="C22" s="117">
+        <f>Assumptions!$C$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="66" t="inlineStr">
+        <is>
+          <t>VOLUME &amp; REVENUE</t>
+        </is>
+      </c>
+      <c r="C24" s="66" t="inlineStr"/>
+      <c r="D24" s="66" t="inlineStr"/>
+      <c r="E24" s="66" t="inlineStr"/>
+      <c r="F24" s="66" t="inlineStr"/>
+      <c r="G24" s="66" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="75" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E25" s="76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="G25" s="76" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>Subscriber rounds (attempts/yr)</t>
+        </is>
+      </c>
+      <c r="E26" s="78">
+        <f>Valuation!C6*$C$22*12</f>
+        <v/>
+      </c>
+      <c r="F26" s="78">
+        <f>Valuation!D6*$C$22*12</f>
+        <v/>
+      </c>
+      <c r="G26" s="78">
+        <f>Valuation!E6*$C$22*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>Simulator challenges</t>
+        </is>
+      </c>
+      <c r="E27" s="117">
+        <f>Simulator!C25</f>
+        <v/>
+      </c>
+      <c r="F27" s="117">
+        <f>Simulator!F25</f>
+        <v/>
+      </c>
+      <c r="G27" s="117">
+        <f>Simulator!G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Gross upsell revenue ($)</t>
+        </is>
+      </c>
+      <c r="E28" s="79">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F28" s="79">
+        <f>F26*$C$16*$C$17+F27*$C$18*$C$19</f>
+        <v/>
+      </c>
+      <c r="G28" s="79">
+        <f>G26*$C$16*$C$17+G27*$C$18*$C$19</f>
+        <v/>
+      </c>
+      <c r="I28" s="115" t="inlineStr">
+        <is>
+          <t>The menu ships with the app build in 2027, so 2026 is set to zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>Revenue to Get Lucky ($)</t>
+        </is>
+      </c>
+      <c r="E29" s="80">
+        <f>E28*$C$20</f>
+        <v/>
+      </c>
+      <c r="F29" s="80">
+        <f>F28*$C$20</f>
+        <v/>
+      </c>
+      <c r="G29" s="80">
+        <f>G28*$C$20</f>
+        <v/>
+      </c>
+      <c r="I29" s="115" t="inlineStr">
+        <is>
+          <t>This row feeds the Valuation tab (2026 = col E, 2029 = col F, 2032 = col G).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>Memo — revenue to Get Lucky (ZAR)</t>
+        </is>
+      </c>
+      <c r="E30" s="81">
+        <f>E29*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="F30" s="81">
+        <f>F29*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="G30" s="81">
+        <f>G29*Assumptions!$C$11</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4058,7 +4555,7 @@
         <v/>
       </c>
       <c r="F6" s="86" t="n"/>
-      <c r="G6" s="102" t="inlineStr">
+      <c r="G6" s="124" t="inlineStr">
         <is>
           <t>2032 extends the Yr3 exit ramp</t>
         </is>
@@ -4083,7 +4580,7 @@
         <v/>
       </c>
       <c r="F7" s="86" t="n"/>
-      <c r="G7" s="102" t="inlineStr">
+      <c r="G7" s="124" t="inlineStr">
         <is>
           <t>Sum of MRR across months 1-12 (actual 2026 revenue)</t>
         </is>
@@ -4108,7 +4605,7 @@
         <v/>
       </c>
       <c r="F8" s="86" t="n"/>
-      <c r="G8" s="102" t="inlineStr">
+      <c r="G8" s="124" t="inlineStr">
         <is>
           <t>The contracted Santam deal, off the monthly build</t>
         </is>
@@ -4133,7 +4630,7 @@
         <v/>
       </c>
       <c r="F9" s="86" t="n"/>
-      <c r="G9" s="102" t="inlineStr">
+      <c r="G9" s="124" t="inlineStr">
         <is>
           <t>Installed courses, membership and the global app subscription, plus contracted South African sponsorship</t>
         </is>
@@ -4158,7 +4655,7 @@
         <v/>
       </c>
       <c r="F10" s="86" t="n"/>
-      <c r="G10" s="102" t="inlineStr">
+      <c r="G10" s="124" t="inlineStr">
         <is>
           <t>From the Simulator tab. Revenue stream 4, live from 2027; integration funded by this round.</t>
         </is>
@@ -4183,141 +4680,145 @@
         <v/>
       </c>
       <c r="F11" s="86" t="n"/>
-      <c r="G11" s="102" t="inlineStr">
+      <c r="G11" s="124" t="inlineStr">
         <is>
           <t>From the Sponsorship tab. The signed Santam deal repeated with an anchor insurer partner per new market.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>In-play upsells ($)</t>
+        </is>
+      </c>
+      <c r="C12" s="118">
+        <f>Upsells!E29</f>
+        <v/>
+      </c>
+      <c r="D12" s="118">
+        <f>Upsells!F29</f>
+        <v/>
+      </c>
+      <c r="E12" s="118">
+        <f>Upsells!G29</f>
+        <v/>
+      </c>
+      <c r="F12" s="86" t="n"/>
+      <c r="G12" s="124" t="inlineStr">
+        <is>
+          <t>From the Upsells tab. Attaches to attempts already counted above — never new volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="119" t="inlineStr">
         <is>
           <t>Total annual revenue ($)</t>
         </is>
       </c>
-      <c r="C12" s="80">
-        <f>C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="80">
-        <f>D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="80">
-        <f>E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="86" t="n"/>
-      <c r="G12" s="102" t="inlineStr">
+      <c r="C13" s="80">
+        <f>C9+C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="80">
+        <f>D9+D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="80">
+        <f>E9+E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="86" t="n"/>
+      <c r="G13" s="124" t="inlineStr">
         <is>
           <t>Drives the valuation walk below.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="91" t="inlineStr">
-        <is>
-          <t>Gross profit — courses &amp; app ($)</t>
-        </is>
-      </c>
-      <c r="C13" s="79">
-        <f>C9*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="D13" s="79">
-        <f>D9*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="E13" s="79">
-        <f>E9*Assumptions!$C$22</f>
-        <v/>
-      </c>
-      <c r="F13" s="86" t="n"/>
-      <c r="G13" s="106" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="67" t="inlineStr">
         <is>
-          <t>EBITDA proxy — courses &amp; app ($)</t>
+          <t>Gross profit — courses &amp; app ($)</t>
         </is>
       </c>
       <c r="C14" s="88">
-        <f>C13-Assumptions!$C$26*12*(C6/$C$6)^Assumptions!$C$27-C9*Assumptions!$C$24</f>
+        <f>C9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="D14" s="88">
-        <f>D13-Assumptions!$C$26*12*(D6/$C$6)^Assumptions!$C$27-D9*Assumptions!$C$24</f>
+        <f>D9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="E14" s="88">
-        <f>E13-Assumptions!$C$26*12*(E6/$C$6)^Assumptions!$C$27-E9*Assumptions!$C$24</f>
+        <f>E9*Assumptions!$C$22</f>
         <v/>
       </c>
       <c r="F14" s="86" t="n"/>
-      <c r="G14" s="102" t="inlineStr">
-        <is>
-          <t>GP less scaled opex less insurance premium. Prize payouts excluded — carried by the insurer.</t>
-        </is>
-      </c>
+      <c r="G14" s="106" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="67" t="inlineStr">
         <is>
-          <t>EBITDA proxy — simulators ($)</t>
+          <t>EBITDA proxy — courses &amp; app ($)</t>
         </is>
       </c>
       <c r="C15" s="88">
-        <f>C10*Simulator!$C$17</f>
+        <f>C14-Assumptions!$C$26*12*(C6/$C$6)^Assumptions!$C$27-C9*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="D15" s="88">
-        <f>D10*Simulator!$C$17</f>
+        <f>D14-Assumptions!$C$26*12*(D6/$C$6)^Assumptions!$C$27-D9*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="E15" s="88">
-        <f>E10*Simulator!$C$17</f>
+        <f>E14-Assumptions!$C$26*12*(E6/$C$6)^Assumptions!$C$27-E9*Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="F15" s="86" t="n"/>
-      <c r="G15" s="92" t="n"/>
+      <c r="G15" s="124" t="inlineStr">
+        <is>
+          <t>GP less scaled opex less insurance premium. Prize payouts excluded — carried by the insurer.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="67" t="inlineStr">
         <is>
-          <t>EBITDA proxy — territory sponsorship ($)</t>
+          <t>EBITDA proxy — simulators ($)</t>
         </is>
       </c>
       <c r="C16" s="88">
-        <f>C11*Sponsorship!$C$22</f>
+        <f>C10*Simulator!$C$17</f>
         <v/>
       </c>
       <c r="D16" s="88">
-        <f>D11*Sponsorship!$C$22</f>
+        <f>D10*Simulator!$C$17</f>
         <v/>
       </c>
       <c r="E16" s="88">
-        <f>E11*Sponsorship!$C$22</f>
+        <f>E10*Simulator!$C$17</f>
         <v/>
       </c>
       <c r="F16" s="86" t="n"/>
       <c r="G16" s="92" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="75" t="inlineStr">
-        <is>
-          <t>EBITDA proxy — total ($)</t>
-        </is>
-      </c>
-      <c r="C17" s="80">
-        <f>C14+C15+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="80">
-        <f>D14+D15+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="80">
-        <f>E14+E15+E16</f>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>EBITDA proxy — territory sponsorship ($)</t>
+        </is>
+      </c>
+      <c r="C17" s="79">
+        <f>C11*Sponsorship!$C$22</f>
+        <v/>
+      </c>
+      <c r="D17" s="79">
+        <f>D11*Sponsorship!$C$22</f>
+        <v/>
+      </c>
+      <c r="E17" s="79">
+        <f>E11*Sponsorship!$C$22</f>
         <v/>
       </c>
       <c r="F17" s="86" t="n"/>
@@ -4326,255 +4827,265 @@
     <row r="18">
       <c r="B18" s="107" t="inlineStr">
         <is>
-          <t>EBITDA margin (% of total revenue)</t>
-        </is>
-      </c>
-      <c r="C18" s="108">
-        <f>IFERROR(C17/C12,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="108">
-        <f>IFERROR(D17/D12,0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="108">
-        <f>IFERROR(E17/E12,0)</f>
+          <t>EBITDA proxy — in-play upsells ($)</t>
+        </is>
+      </c>
+      <c r="C18" s="125">
+        <f>C12*Upsells!$C$21</f>
+        <v/>
+      </c>
+      <c r="D18" s="125">
+        <f>D12*Upsells!$C$21</f>
+        <v/>
+      </c>
+      <c r="E18" s="125">
+        <f>E12*Upsells!$C$21</f>
         <v/>
       </c>
       <c r="F18" s="95" t="n"/>
       <c r="G18" s="95" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="86" t="n"/>
-      <c r="C19" s="109" t="n"/>
-      <c r="D19" s="109" t="n"/>
-      <c r="E19" s="109" t="n"/>
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>EBITDA proxy — total ($)</t>
+        </is>
+      </c>
+      <c r="C19" s="80">
+        <f>C15+C16+C17+C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="80">
+        <f>D15+D16+D17+D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="80">
+        <f>E15+E16+E17+E18</f>
+        <v/>
+      </c>
       <c r="F19" s="86" t="n"/>
       <c r="G19" s="106" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="66" t="inlineStr">
+      <c r="B20" s="107" t="inlineStr">
+        <is>
+          <t>EBITDA margin (% of total revenue)</t>
+        </is>
+      </c>
+      <c r="C20" s="108">
+        <f>IFERROR(C19/C13,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="108">
+        <f>IFERROR(D19/D13,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="108">
+        <f>IFERROR(E19/E13,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="95" t="n"/>
+      <c r="G20" s="95" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="86" t="n"/>
+      <c r="C21" s="121" t="n"/>
+      <c r="D21" s="121" t="n"/>
+      <c r="E21" s="121" t="n"/>
+      <c r="F21" s="86" t="n"/>
+      <c r="G21" s="106" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>VALUATION WALK</t>
         </is>
       </c>
-      <c r="C20" s="110" t="inlineStr"/>
-      <c r="D20" s="110" t="inlineStr"/>
-      <c r="E20" s="110" t="inlineStr"/>
-      <c r="F20" s="66" t="inlineStr"/>
-      <c r="G20" s="66" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="67" t="inlineStr">
-        <is>
-          <t>Implied revenue multiple</t>
-        </is>
-      </c>
-      <c r="C21" s="83">
-        <f>Assumptions!$C$8/C12</f>
-        <v/>
-      </c>
-      <c r="D21" s="83">
-        <f>Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="E21" s="83">
-        <f>Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="F21" s="86" t="n"/>
-      <c r="G21" s="102" t="inlineStr">
-        <is>
-          <t>Today solved to the post-money floor; out-years from Assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="107" t="inlineStr">
-        <is>
-          <t>Valuation milestone — pitch ($)</t>
-        </is>
-      </c>
-      <c r="C22" s="79">
-        <f>Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="D22" s="79">
-        <f>Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E22" s="79">
-        <f>Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="F22" s="86" t="n"/>
-      <c r="G22" s="102" t="inlineStr">
-        <is>
-          <t>Headline figures from the pitch: R53.3m / R135.2m / R744m.</t>
-        </is>
-      </c>
+      <c r="C22" s="110" t="inlineStr"/>
+      <c r="D22" s="110" t="inlineStr"/>
+      <c r="E22" s="110" t="inlineStr"/>
+      <c r="F22" s="66" t="inlineStr"/>
+      <c r="G22" s="66" t="inlineStr"/>
     </row>
     <row r="23" ht="13" customFormat="1" customHeight="1" s="35">
       <c r="B23" s="67" t="inlineStr">
         <is>
-          <t>Valuation — model-implied ($)</t>
-        </is>
-      </c>
-      <c r="C23" s="79">
-        <f>C12*C21</f>
-        <v/>
-      </c>
-      <c r="D23" s="79">
-        <f>D12*D21</f>
-        <v/>
-      </c>
-      <c r="E23" s="79">
-        <f>E12*E21</f>
+          <t>Implied revenue multiple</t>
+        </is>
+      </c>
+      <c r="C23" s="83">
+        <f>Assumptions!$C$8/C13</f>
+        <v/>
+      </c>
+      <c r="D23" s="83">
+        <f>Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="E23" s="83">
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
       <c r="F23" s="86" t="n"/>
-      <c r="G23" s="102" t="inlineStr">
-        <is>
-          <t>Sanity check: does the ramp x multiple reach the milestone?</t>
+      <c r="G23" s="124" t="inlineStr">
+        <is>
+          <t>Today solved to the post-money floor; out-years from Assumptions.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="13" customFormat="1" customHeight="1" s="35">
-      <c r="B24" s="86" t="n"/>
-      <c r="C24" s="111" t="n"/>
-      <c r="D24" s="111" t="n"/>
-      <c r="E24" s="111" t="n"/>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>Valuation milestone — pitch ($)</t>
+        </is>
+      </c>
+      <c r="C24" s="79">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="D24" s="79">
+        <f>Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E24" s="79">
+        <f>Assumptions!$C$33</f>
+        <v/>
+      </c>
       <c r="F24" s="86" t="n"/>
-      <c r="G24" s="86" t="n"/>
+      <c r="G24" s="124" t="inlineStr">
+        <is>
+          <t>Headline figures from the pitch: R53.3m / R147m / R807m.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="13" customFormat="1" customHeight="1" s="35">
       <c r="B25" s="67" t="inlineStr">
         <is>
-          <t>Memo — model valuation in ZAR</t>
-        </is>
-      </c>
-      <c r="C25" s="81">
-        <f>C23*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="D25" s="81">
-        <f>D23*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="E25" s="81">
-        <f>E23*Assumptions!$C$11</f>
+          <t>Valuation — model-implied ($)</t>
+        </is>
+      </c>
+      <c r="C25" s="79">
+        <f>C13*C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="79">
+        <f>D13*D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="79">
+        <f>E13*E23</f>
         <v/>
       </c>
       <c r="F25" s="86" t="n"/>
-      <c r="G25" s="106" t="n"/>
+      <c r="G25" s="124" t="inlineStr">
+        <is>
+          <t>Sanity check: does the ramp x multiple reach the milestone?</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="14" customFormat="1" customHeight="1" s="46">
-      <c r="B26" s="67" t="inlineStr">
-        <is>
-          <t>Memo — pitch milestone in ZAR</t>
-        </is>
-      </c>
-      <c r="C26" s="81">
-        <f>C22*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="D26" s="81">
-        <f>D22*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="E26" s="81">
-        <f>E22*Assumptions!$C$11</f>
-        <v/>
-      </c>
+      <c r="B26" s="86" t="n"/>
+      <c r="C26" s="111" t="n"/>
+      <c r="D26" s="111" t="n"/>
+      <c r="E26" s="111" t="n"/>
       <c r="F26" s="86" t="n"/>
       <c r="G26" s="86" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="107" t="inlineStr">
         <is>
-          <t>Memo — revenue by stream in ZAR</t>
+          <t>Memo — model valuation in ZAR</t>
         </is>
       </c>
       <c r="C27" s="112">
-        <f>C12*Assumptions!$C$11</f>
+        <f>C25*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D27" s="112">
-        <f>D12*Assumptions!$C$11</f>
+        <f>D25*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="E27" s="112">
-        <f>E12*Assumptions!$C$11</f>
+        <f>E25*Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="F27" s="95" t="n"/>
-      <c r="G27" s="102" t="inlineStr">
-        <is>
-          <t>Total revenue in rand. Stream split is rows 9-11 above.</t>
-        </is>
-      </c>
+      <c r="G27" s="106" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="86" t="n"/>
-      <c r="C28" s="113" t="n"/>
-      <c r="D28" s="86" t="n"/>
-      <c r="E28" s="86" t="n"/>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Memo — pitch milestone in ZAR</t>
+        </is>
+      </c>
+      <c r="C28" s="122">
+        <f>C24*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="D28" s="81">
+        <f>D24*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="E28" s="81">
+        <f>E24*Assumptions!$C$11</f>
+        <v/>
+      </c>
       <c r="F28" s="86" t="n"/>
       <c r="G28" s="86" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="66" t="inlineStr">
-        <is>
-          <t>WHY 6x REVENUE AT EXIT (2032)</t>
-        </is>
-      </c>
-      <c r="C29" s="66" t="inlineStr"/>
-      <c r="D29" s="66" t="inlineStr"/>
-      <c r="E29" s="66" t="inlineStr"/>
-      <c r="F29" s="66" t="inlineStr"/>
-      <c r="G29" s="66" t="inlineStr"/>
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>Memo — revenue by stream in ZAR</t>
+        </is>
+      </c>
+      <c r="C29" s="112">
+        <f>C13*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="D29" s="112">
+        <f>D13*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="E29" s="112">
+        <f>E13*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="F29" s="95" t="n"/>
+      <c r="G29" s="124" t="inlineStr">
+        <is>
+          <t>Total revenue in rand. Stream split is rows 9-12 above.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>Engaged subscriber database</t>
-        </is>
-      </c>
-      <c r="C30" s="114" t="inlineStr">
-        <is>
-          <t>Recurring golfers opted into a high-intent niche product are the core asset — a clean, targetable distribution channel for golf brands, media partners and sponsors. The valuation reflects the database itself, not just the topline.</t>
-        </is>
-      </c>
+      <c r="B30" s="86" t="n"/>
+      <c r="C30" s="113" t="n"/>
       <c r="D30" s="86" t="n"/>
       <c r="E30" s="86" t="n"/>
       <c r="F30" s="86" t="n"/>
       <c r="G30" s="86" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="67" t="inlineStr">
-        <is>
-          <t>Four revenue streams, one product</t>
-        </is>
-      </c>
-      <c r="C31" s="114" t="inlineStr">
-        <is>
-          <t>Installed courses, membership, the global app subscription and simulators sell the same insured challenge through four channels, with sponsorship attached to each territory. Diversified revenue on one cost base.</t>
-        </is>
-      </c>
-      <c r="D31" s="86" t="n"/>
-      <c r="E31" s="86" t="n"/>
-      <c r="F31" s="86" t="n"/>
-      <c r="G31" s="86" t="n"/>
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>WHY 6x REVENUE AT EXIT (2032)</t>
+        </is>
+      </c>
+      <c r="C31" s="66" t="inlineStr"/>
+      <c r="D31" s="66" t="inlineStr"/>
+      <c r="E31" s="66" t="inlineStr"/>
+      <c r="F31" s="66" t="inlineStr"/>
+      <c r="G31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="B32" s="67" t="inlineStr">
         <is>
-          <t>Strategic partner optionality</t>
-        </is>
-      </c>
-      <c r="C32" s="114" t="inlineStr">
-        <is>
-          <t>At scale the platform unlocks multiple exit paths: license access to a golf brand, co-brand prize pools with a tour or media rights holder, integrate with a sportsbook, or sell outright to a sports-tech acquirer.</t>
+          <t>Engaged subscriber database</t>
+        </is>
+      </c>
+      <c r="C32" s="126" t="inlineStr">
+        <is>
+          <t>Recurring golfers opted into a high-intent niche product are the core asset — a clean, targetable distribution channel for golf brands, media partners and sponsors. The valuation reflects the database itself, not just the topline.</t>
         </is>
       </c>
       <c r="D32" s="86" t="n"/>
@@ -4585,12 +5096,12 @@
     <row r="33">
       <c r="B33" s="67" t="inlineStr">
         <is>
-          <t>Comparable engaged communities</t>
-        </is>
-      </c>
-      <c r="C33" s="114" t="inlineStr">
-        <is>
-          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) have transacted in the 5-10x revenue range at similar scale. 6x sits mid-band.</t>
+          <t>Four rungs plus an upsell menu</t>
+        </is>
+      </c>
+      <c r="C33" s="126" t="inlineStr">
+        <is>
+          <t>Installed courses, membership, the global app subscription and simulators sell the same insured challenge through four channels, with sponsorship attached to each territory. Diversified revenue on one cost base.</t>
         </is>
       </c>
       <c r="D33" s="86" t="n"/>
@@ -4601,12 +5112,12 @@
     <row r="34">
       <c r="B34" s="67" t="inlineStr">
         <is>
-          <t>Risk to the multiple</t>
-        </is>
-      </c>
-      <c r="C34" s="114" t="inlineStr">
-        <is>
-          <t>If growth stalls the multiple compresses toward pure SaaS (3-4x), landing 2032 at R372-496m rather than R744m.</t>
+          <t>Strategic partner optionality</t>
+        </is>
+      </c>
+      <c r="C34" s="126" t="inlineStr">
+        <is>
+          <t>At scale the platform unlocks multiple exit paths: license access to a golf brand, co-brand prize pools with a tour or media rights holder, integrate with a sportsbook, or sell outright to a sports-tech acquirer.</t>
         </is>
       </c>
       <c r="D34" s="86" t="n"/>
@@ -4617,12 +5128,12 @@
     <row r="35">
       <c r="B35" s="67" t="inlineStr">
         <is>
-          <t>Risk to the simulator stream</t>
-        </is>
-      </c>
-      <c r="C35" s="114" t="inlineStr">
-        <is>
-          <t>Simulator revenue depends on concluding operator agreements, which are not yet signed as at August 2026. Ernie Els holds direct relationships with the target operators; the integration this round funds is what makes Get Lucky ready to sign. Set the attach rate to zero on the Simulator tab to model the group without the stream.</t>
+          <t>Comparable engaged communities</t>
+        </is>
+      </c>
+      <c r="C35" s="126" t="inlineStr">
+        <is>
+          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) have transacted in the 5-10x revenue range at similar scale. 6x sits mid-band.</t>
         </is>
       </c>
       <c r="D35" s="86" t="n"/>
@@ -4633,14 +5144,82 @@
     <row r="36">
       <c r="B36" s="67" t="inlineStr">
         <is>
+          <t>Risk to the multiple</t>
+        </is>
+      </c>
+      <c r="C36" s="126" t="inlineStr">
+        <is>
+          <t>If growth stalls the multiple compresses toward pure SaaS (3-4x), landing 2032 at R404-538m rather than R807m.</t>
+        </is>
+      </c>
+      <c r="D36" s="86" t="n"/>
+      <c r="E36" s="86" t="n"/>
+      <c r="F36" s="86" t="n"/>
+      <c r="G36" s="86" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>Risk to the simulator stream</t>
+        </is>
+      </c>
+      <c r="C37" s="126" t="inlineStr">
+        <is>
+          <t>Simulator revenue depends on concluding operator agreements, which are not yet signed as at August 2026. Ernie Els holds direct relationships with the target operators; the integration this round funds is what makes Get Lucky ready to sign. Set the attach rate to zero on the Simulator tab to model the group without the stream.</t>
+        </is>
+      </c>
+      <c r="D37" s="86" t="n"/>
+      <c r="E37" s="86" t="n"/>
+      <c r="F37" s="86" t="n"/>
+      <c r="G37" s="86" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="67" t="inlineStr">
+        <is>
           <t>Risk to territory sponsorship</t>
         </is>
       </c>
-      <c r="C36" s="114" t="inlineStr">
+      <c r="C38" s="126" t="inlineStr">
         <is>
           <t>South African sponsorship is contracted. New-territory anchor partners are appointed as each market opens and are not yet in place. Per-territory figures are live inputs on the Sponsorship tab.</t>
         </is>
       </c>
+      <c r="D38" s="86" t="n"/>
+      <c r="E38" s="86" t="n"/>
+      <c r="F38" s="86" t="n"/>
+      <c r="G38" s="86" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>Risk to upsell attach</t>
+        </is>
+      </c>
+      <c r="C39" s="126" t="inlineStr">
+        <is>
+          <t>Attach rates are modelled, not observed — the menu ships in 2027. They are set against the price point of the underlying entry (12% at $5 on course and app, 5% at $2 in simulators) and are live inputs on the Upsells tab.</t>
+        </is>
+      </c>
+      <c r="D39" s="86" t="n"/>
+      <c r="E39" s="86" t="n"/>
+      <c r="F39" s="86" t="n"/>
+      <c r="G39" s="86" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="86" t="n"/>
+      <c r="C40" s="86" t="n"/>
+      <c r="D40" s="86" t="n"/>
+      <c r="E40" s="86" t="n"/>
+      <c r="F40" s="86" t="n"/>
+      <c r="G40" s="86" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="86" t="n"/>
+      <c r="C41" s="86" t="n"/>
+      <c r="D41" s="86" t="n"/>
+      <c r="E41" s="86" t="n"/>
+      <c r="F41" s="86" t="n"/>
+      <c r="G41" s="86" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4652,7 +5231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4706,15 +5285,15 @@
         </is>
       </c>
       <c r="C6" s="44">
-        <f>Valuation!C22</f>
+        <f>Valuation!C24</f>
         <v/>
       </c>
       <c r="D6" s="44">
-        <f>Valuation!D22</f>
+        <f>Valuation!D24</f>
         <v/>
       </c>
       <c r="E6" s="44">
-        <f>Valuation!E22</f>
+        <f>Valuation!E24</f>
         <v/>
       </c>
       <c r="F6" s="20" t="inlineStr">

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -408,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -614,6 +614,12 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3060,7 +3066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I38"/>
+  <dimension ref="B2:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3070,8 +3076,9 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -3108,7 +3115,7 @@
           <t>LAUNCHING 2027</t>
         </is>
       </c>
-      <c r="E6" s="115" t="inlineStr">
+      <c r="E6" s="127" t="inlineStr">
         <is>
           <t>Revenue stream 4 of 4. Integration funded by this round (20% of the R8m raise).</t>
         </is>
@@ -3125,7 +3132,7 @@
           <t>Golfzon</t>
         </is>
       </c>
-      <c r="E7" s="115" t="inlineStr">
+      <c r="E7" s="127" t="inlineStr">
         <is>
           <t>6,500+ venues, ~60% of the global commercial simulator market (Forbes / Seoulz).</t>
         </is>
@@ -3142,7 +3149,7 @@
           <t>Ernie Els — direct relationships</t>
         </is>
       </c>
-      <c r="E8" s="115" t="inlineStr">
+      <c r="E8" s="127" t="inlineStr">
         <is>
           <t>Ernie Els has direct relationships with the target operators and opens the door himself. Access, not a contract.</t>
         </is>
@@ -3183,7 +3190,7 @@
       <c r="C11" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="115" t="inlineStr">
+      <c r="E11" s="127" t="inlineStr">
         <is>
           <t>Price per in-sim challenge, charged inside the operator software.</t>
         </is>
@@ -3198,7 +3205,7 @@
       <c r="C12" s="70" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="115" t="inlineStr">
+      <c r="E12" s="127" t="inlineStr">
         <is>
           <t>Paid by the insurer on a verified ace. Get Lucky carries no prize risk.</t>
         </is>
@@ -3213,7 +3220,7 @@
       <c r="C13" s="71" t="n">
         <v>0.46</v>
       </c>
-      <c r="E13" s="115" t="inlineStr">
+      <c r="E13" s="127" t="inlineStr">
         <is>
           <t>Residual after operator and insurer shares. Key commercial assumption — confirm on signature.</t>
         </is>
@@ -3228,7 +3235,7 @@
       <c r="C14" s="71" t="n">
         <v>0.3</v>
       </c>
-      <c r="E14" s="115" t="inlineStr">
+      <c r="E14" s="127" t="inlineStr">
         <is>
           <t>More than a course 10%: the operator brings venues, software surface and distribution; Get Lucky installs no hardware.</t>
         </is>
@@ -3243,7 +3250,7 @@
       <c r="C15" s="72" t="n">
         <v>0.24</v>
       </c>
-      <c r="E15" s="115" t="inlineStr">
+      <c r="E15" s="127" t="inlineStr">
         <is>
           <t>Held identical to the on-course insurance premium assumption.</t>
         </is>
@@ -3259,7 +3266,7 @@
         <f>C13+C14+C15</f>
         <v/>
       </c>
-      <c r="E16" s="115" t="inlineStr">
+      <c r="E16" s="127" t="inlineStr">
         <is>
           <t>Must read 100.0%.</t>
         </is>
@@ -3274,7 +3281,7 @@
       <c r="C17" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="E17" s="115" t="inlineStr">
+      <c r="E17" s="127" t="inlineStr">
         <is>
           <t>Software-only channel: no cameras, no installation, no course revenue share. After integration engineering, operator marketing support and platform ops.</t>
         </is>
@@ -3298,7 +3305,7 @@
       <c r="C20" s="74" t="n">
         <v>94000000</v>
       </c>
-      <c r="E20" s="115" t="inlineStr">
+      <c r="E20" s="127" t="inlineStr">
         <is>
           <t>Source: GOLF.com — ~94M rounds logged on Golfzon simulators in South Korea in a single year. Korea ONLY: Golfzon venues elsewhere and all other operators are excluded from this model.</t>
         </is>
@@ -3369,7 +3376,7 @@
       <c r="G24" s="77" t="n">
         <v>0.04</v>
       </c>
-      <c r="I24" s="115" t="inlineStr">
+      <c r="I24" s="127" t="inlineStr">
         <is>
           <t>2026 is an integration year — no revenue modelled.</t>
         </is>
@@ -3455,7 +3462,7 @@
         <f>G26*$C$13</f>
         <v/>
       </c>
-      <c r="I27" s="115" t="inlineStr">
+      <c r="I27" s="127" t="inlineStr">
         <is>
           <t>This row feeds the Valuation tab (2026 = col C, 2029 = col F, 2032 = col G).</t>
         </is>
@@ -3518,7 +3525,7 @@
     <row r="31">
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>SENSITIVITY — 2029</t>
+          <t>ADOPTION RANGE — 2029</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr"/>
@@ -3526,6 +3533,9 @@
       <c r="E31" s="66" t="inlineStr"/>
       <c r="F31" s="66" t="inlineStr"/>
       <c r="G31" s="66" t="inlineStr"/>
+      <c r="H31" s="66" t="inlineStr"/>
+      <c r="I31" s="66" t="inlineStr"/>
+      <c r="J31" s="86" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="76" t="inlineStr">
@@ -3540,151 +3550,184 @@
       </c>
       <c r="D32" s="76" t="inlineStr">
         <is>
+          <t>Upsell revenue ($)</t>
+        </is>
+      </c>
+      <c r="E32" s="76" t="inlineStr">
+        <is>
           <t>Total revenue ($)</t>
         </is>
       </c>
-      <c r="E32" s="76" t="inlineStr">
+      <c r="F32" s="76" t="inlineStr">
         <is>
           <t>Valuation ($)</t>
         </is>
       </c>
-      <c r="F32" s="76" t="inlineStr">
+      <c r="G32" s="76" t="inlineStr">
         <is>
           <t>Valuation (ZAR)</t>
         </is>
       </c>
-      <c r="G32" s="76" t="inlineStr">
+      <c r="H32" s="76" t="inlineStr">
         <is>
           <t>Investor multiple</t>
         </is>
       </c>
+      <c r="I32" s="86" t="n"/>
+      <c r="J32" s="86" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="77" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C33" s="79">
         <f>$C$20*B33*$C$11*$C$13</f>
         <v/>
       </c>
       <c r="D33" s="79">
-        <f>Valuation!$D$9+C33</f>
+        <f>(Valuation!$D$6*Upsells!$C$22*12*Upsells!$C$16*Upsells!$C$17+$C$20*B33*Upsells!$C$18*Upsells!$C$19)*Upsells!$C$20</f>
         <v/>
       </c>
       <c r="E33" s="79">
-        <f>D33*Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F33" s="82">
-        <f>E33*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="G33" s="98">
-        <f>E33/Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="I33" s="115" t="inlineStr">
-        <is>
-          <t>no adoption — model floor</t>
+        <f>Valuation!$D$9+Valuation!$D$11+C33+D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="79">
+        <f>E33*Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="G33" s="82">
+        <f>F33*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="H33" s="98">
+        <f>F33/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="I33" s="106" t="n"/>
+      <c r="J33" s="127" t="inlineStr">
+        <is>
+          <t>conservative</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="77" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="C34" s="79">
         <f>$C$20*B34*$C$11*$C$13</f>
         <v/>
       </c>
       <c r="D34" s="79">
-        <f>Valuation!$D$9+C34</f>
+        <f>(Valuation!$D$6*Upsells!$C$22*12*Upsells!$C$16*Upsells!$C$17+$C$20*B34*Upsells!$C$18*Upsells!$C$19)*Upsells!$C$20</f>
         <v/>
       </c>
       <c r="E34" s="79">
-        <f>D34*Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F34" s="82">
-        <f>E34*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="G34" s="98">
-        <f>E34/Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="I34" s="115" t="inlineStr">
-        <is>
-          <t>conservative</t>
+        <f>Valuation!$D$9+Valuation!$D$11+C34+D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="79">
+        <f>E34*Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="G34" s="82">
+        <f>F34*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="H34" s="98">
+        <f>F34/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="I34" s="106" t="n"/>
+      <c r="J34" s="127" t="inlineStr">
+        <is>
+          <t>the plan</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="77" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="C35" s="79">
         <f>$C$20*B35*$C$11*$C$13</f>
         <v/>
       </c>
       <c r="D35" s="79">
-        <f>Valuation!$D$9+C35</f>
+        <f>(Valuation!$D$6*Upsells!$C$22*12*Upsells!$C$16*Upsells!$C$17+$C$20*B35*Upsells!$C$18*Upsells!$C$19)*Upsells!$C$20</f>
         <v/>
       </c>
       <c r="E35" s="79">
-        <f>D35*Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F35" s="82">
-        <f>E35*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="G35" s="98">
-        <f>E35/Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="I35" s="115" t="inlineStr">
-        <is>
-          <t>the plan</t>
+        <f>Valuation!$D$9+Valuation!$D$11+C35+D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="79">
+        <f>E35*Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="G35" s="82">
+        <f>F35*Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="H35" s="98">
+        <f>F35/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="I35" s="106" t="n"/>
+      <c r="J35" s="127" t="inlineStr">
+        <is>
+          <t>strong adoption</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="77" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C36" s="79">
-        <f>$C$20*B36*$C$11*$C$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="79">
-        <f>Valuation!$D$9+C36</f>
-        <v/>
-      </c>
-      <c r="E36" s="79">
-        <f>D36*Assumptions!$C$30</f>
-        <v/>
-      </c>
-      <c r="F36" s="82">
-        <f>E36*Assumptions!$C$11</f>
-        <v/>
-      </c>
-      <c r="G36" s="98">
-        <f>E36/Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="I36" s="115" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
+      <c r="B36" s="128" t="n"/>
+      <c r="C36" s="129" t="n"/>
+      <c r="D36" s="129" t="n"/>
+      <c r="E36" s="129" t="n"/>
+      <c r="F36" s="111" t="n"/>
+      <c r="G36" s="130" t="n"/>
+      <c r="H36" s="86" t="n"/>
+      <c r="I36" s="106" t="n"/>
+      <c r="J36" s="86" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="86" t="n"/>
+      <c r="C37" s="86" t="n"/>
+      <c r="D37" s="86" t="n"/>
+      <c r="E37" s="86" t="n"/>
+      <c r="F37" s="86" t="n"/>
+      <c r="G37" s="86" t="n"/>
+      <c r="H37" s="86" t="n"/>
+      <c r="I37" s="86" t="n"/>
+      <c r="J37" s="86" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="115" t="inlineStr">
-        <is>
-          <t>Investor multiple = company valuation at the 2029 milestone divided by the post-money valuation of this round. Attach rate is a live input — set it to zero to model the group without the simulator stream.</t>
-        </is>
-      </c>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>The adoption range around the plan, with courses &amp; app and territory sponsorship held at plan. Upsell revenue moves with simulator volume, so it is recomputed per row rather than held flat. Investor multiple = company valuation at the 2029 milestone divided by the post-money valuation of this round.</t>
+        </is>
+      </c>
+      <c r="C38" s="86" t="n"/>
+      <c r="D38" s="86" t="n"/>
+      <c r="E38" s="86" t="n"/>
+      <c r="F38" s="86" t="n"/>
+      <c r="G38" s="86" t="n"/>
+      <c r="H38" s="86" t="n"/>
+      <c r="I38" s="86" t="n"/>
+      <c r="J38" s="86" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="86" t="n"/>
+      <c r="C39" s="86" t="n"/>
+      <c r="D39" s="86" t="n"/>
+      <c r="E39" s="86" t="n"/>
+      <c r="F39" s="86" t="n"/>
+      <c r="G39" s="86" t="n"/>
+      <c r="H39" s="86" t="n"/>
+      <c r="I39" s="86" t="n"/>
+      <c r="J39" s="86" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3748,7 +3791,7 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="E6" s="115" t="inlineStr">
+      <c r="E6" s="127" t="inlineStr">
         <is>
           <t>Sponsorship is the one line in the plan that was signed rather than forecast.</t>
         </is>
@@ -3787,7 +3830,7 @@
       <c r="C9" s="82" t="n">
         <v>9000000</v>
       </c>
-      <c r="E9" s="115" t="inlineStr">
+      <c r="E9" s="127" t="inlineStr">
         <is>
           <t>R9m over three years, in a market of roughly 150,000 golfers.</t>
         </is>
@@ -3814,14 +3857,14 @@
       <c r="C11" s="78" t="n">
         <v>150000</v>
       </c>
-      <c r="E11" s="115" t="inlineStr">
+      <c r="E11" s="127" t="inlineStr">
         <is>
           <t>The insurer who underwrites the prize is the natural sponsor of it — which is why the deal was signable in a small market and why it repeats in large ones.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="115" t="inlineStr">
+      <c r="B13" s="127" t="inlineStr">
         <is>
           <t>South African sponsorship already sits in the "Sponsorship revenue" row of the Valuation tab, off the monthly build. This tab models NEW territories only, so nothing is double-counted.</t>
         </is>
@@ -3894,7 +3937,7 @@
       <c r="G17" s="104" t="n">
         <v>4000000</v>
       </c>
-      <c r="I17" s="115" t="inlineStr">
+      <c r="I17" s="127" t="inlineStr">
         <is>
           <t>Live input — set each territory to what you believe.</t>
         </is>
@@ -3985,7 +4028,7 @@
         <f>G20/Assumptions!$C$11</f>
         <v/>
       </c>
-      <c r="I21" s="115" t="inlineStr">
+      <c r="I21" s="127" t="inlineStr">
         <is>
           <t>This row feeds the Valuation tab (2026 = col E, 2029 = col F, 2032 = col G).</t>
         </is>
@@ -4000,14 +4043,14 @@
       <c r="C22" s="71" t="n">
         <v>0.6</v>
       </c>
-      <c r="E22" s="115" t="inlineStr">
+      <c r="E22" s="127" t="inlineStr">
         <is>
           <t>After local activation and partner servicing cost.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="115" t="inlineStr">
+      <c r="B24" s="127" t="inlineStr">
         <is>
           <t>Every new-territory figure is set BELOW the South African run-rate at entry, in markets many times its size. Sponsorship is negotiated and lumpy: a linear scale off golfer counts would produce numbers no sponsor would sign. New-territory partners are appointed as each market opens and are not yet in place.</t>
         </is>
@@ -4053,7 +4096,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="115" t="inlineStr">
+      <c r="B4" s="127" t="inlineStr">
         <is>
           <t>Sold AFTER the entry, when the golfer has already paid and is standing over the ball. Upsells attach to attempts already in the model — they never create new volume, so there is no double-count.</t>
         </is>
@@ -4109,7 +4152,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E8" s="123" t="inlineStr">
+      <c r="E8" s="126" t="inlineStr">
         <is>
           <t>Trade up mid-round to a shot at a $100,000 insured prize instead of the standard pot.</t>
         </is>
@@ -4131,7 +4174,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" s="123" t="inlineStr">
+      <c r="E9" s="126" t="inlineStr">
         <is>
           <t>Doubles the prize if the shot goes in. Cheapest yes on the menu, highest attach.</t>
         </is>
@@ -4153,7 +4196,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E10" s="123" t="inlineStr">
+      <c r="E10" s="126" t="inlineStr">
         <is>
           <t>Three swings for the price of two. More attempts per visit, same prize exposure.</t>
         </is>
@@ -4175,7 +4218,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="123" t="inlineStr">
+      <c r="E11" s="126" t="inlineStr">
         <is>
           <t>Guaranteed prize inside three feet — monetises the 12,499 shots in 12,500 that are not an ace.</t>
         </is>
@@ -4197,7 +4240,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E12" s="123" t="inlineStr">
+      <c r="E12" s="126" t="inlineStr">
         <is>
           <t>The produced clip, scored and branded. No insurance component: pure margin, and every share is marketing.</t>
         </is>
@@ -4219,7 +4262,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E13" s="123" t="inlineStr">
+      <c r="E13" s="126" t="inlineStr">
         <is>
           <t>A fourball buys in, closest to the pin takes the pot, Get Lucky takes a fee.</t>
         </is>
@@ -4246,7 +4289,7 @@
       <c r="C16" s="71" t="n">
         <v>0.12</v>
       </c>
-      <c r="I16" s="115" t="inlineStr">
+      <c r="I16" s="127" t="inlineStr">
         <is>
           <t>Share of subscriber rounds that buy at least one upsell. This golfer already pays ~R200 a swing.</t>
         </is>
@@ -4261,7 +4304,7 @@
       <c r="C17" s="116" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="115" t="inlineStr">
+      <c r="I17" s="127" t="inlineStr">
         <is>
           <t>Blend across the menu on an attaching entry.</t>
         </is>
@@ -4276,7 +4319,7 @@
       <c r="C18" s="71" t="n">
         <v>0.05</v>
       </c>
-      <c r="I18" s="115" t="inlineStr">
+      <c r="I18" s="127" t="inlineStr">
         <is>
           <t>Lower: the base simulator entry is $1, so the ask has to be smaller.</t>
         </is>
@@ -4291,7 +4334,7 @@
       <c r="C19" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="115" t="inlineStr">
+      <c r="I19" s="127" t="inlineStr">
         <is>
           <t>Blend across the menu inside a simulator.</t>
         </is>
@@ -4306,7 +4349,7 @@
       <c r="C20" s="71" t="n">
         <v>0.55</v>
       </c>
-      <c r="I20" s="115" t="inlineStr">
+      <c r="I20" s="127" t="inlineStr">
         <is>
           <t>After course or operator share and insurance. Higher than the 46% simulator entry share because part of the menu (highlight reel, group pot) carries no insurance.</t>
         </is>
@@ -4321,7 +4364,7 @@
       <c r="C21" s="71" t="n">
         <v>0.65</v>
       </c>
-      <c r="I21" s="115" t="inlineStr">
+      <c r="I21" s="127" t="inlineStr">
         <is>
           <t>Sold through the existing checkout: no hardware, no new venue cost.</t>
         </is>
@@ -4428,7 +4471,7 @@
         <f>G26*$C$16*$C$17+G27*$C$18*$C$19</f>
         <v/>
       </c>
-      <c r="I28" s="115" t="inlineStr">
+      <c r="I28" s="127" t="inlineStr">
         <is>
           <t>The menu ships with the app build in 2027, so 2026 is set to zero.</t>
         </is>
@@ -4452,7 +4495,7 @@
         <f>G28*$C$20</f>
         <v/>
       </c>
-      <c r="I29" s="115" t="inlineStr">
+      <c r="I29" s="127" t="inlineStr">
         <is>
           <t>This row feeds the Valuation tab (2026 = col E, 2029 = col F, 2032 = col G).</t>
         </is>
@@ -4555,7 +4598,7 @@
         <v/>
       </c>
       <c r="F6" s="86" t="n"/>
-      <c r="G6" s="124" t="inlineStr">
+      <c r="G6" s="127" t="inlineStr">
         <is>
           <t>2032 extends the Yr3 exit ramp</t>
         </is>
@@ -4580,7 +4623,7 @@
         <v/>
       </c>
       <c r="F7" s="86" t="n"/>
-      <c r="G7" s="124" t="inlineStr">
+      <c r="G7" s="127" t="inlineStr">
         <is>
           <t>Sum of MRR across months 1-12 (actual 2026 revenue)</t>
         </is>
@@ -4605,7 +4648,7 @@
         <v/>
       </c>
       <c r="F8" s="86" t="n"/>
-      <c r="G8" s="124" t="inlineStr">
+      <c r="G8" s="127" t="inlineStr">
         <is>
           <t>The contracted Santam deal, off the monthly build</t>
         </is>
@@ -4630,7 +4673,7 @@
         <v/>
       </c>
       <c r="F9" s="86" t="n"/>
-      <c r="G9" s="124" t="inlineStr">
+      <c r="G9" s="127" t="inlineStr">
         <is>
           <t>Installed courses, membership and the global app subscription, plus contracted South African sponsorship</t>
         </is>
@@ -4655,7 +4698,7 @@
         <v/>
       </c>
       <c r="F10" s="86" t="n"/>
-      <c r="G10" s="124" t="inlineStr">
+      <c r="G10" s="127" t="inlineStr">
         <is>
           <t>From the Simulator tab. Revenue stream 4, live from 2027; integration funded by this round.</t>
         </is>
@@ -4680,7 +4723,7 @@
         <v/>
       </c>
       <c r="F11" s="86" t="n"/>
-      <c r="G11" s="124" t="inlineStr">
+      <c r="G11" s="127" t="inlineStr">
         <is>
           <t>From the Sponsorship tab. The signed Santam deal repeated with an anchor insurer partner per new market.</t>
         </is>
@@ -4705,7 +4748,7 @@
         <v/>
       </c>
       <c r="F12" s="86" t="n"/>
-      <c r="G12" s="124" t="inlineStr">
+      <c r="G12" s="127" t="inlineStr">
         <is>
           <t>From the Upsells tab. Attaches to attempts already counted above — never new volume.</t>
         </is>
@@ -4730,7 +4773,7 @@
         <v/>
       </c>
       <c r="F13" s="86" t="n"/>
-      <c r="G13" s="124" t="inlineStr">
+      <c r="G13" s="127" t="inlineStr">
         <is>
           <t>Drives the valuation walk below.</t>
         </is>
@@ -4776,7 +4819,7 @@
         <v/>
       </c>
       <c r="F15" s="86" t="n"/>
-      <c r="G15" s="124" t="inlineStr">
+      <c r="G15" s="127" t="inlineStr">
         <is>
           <t>GP less scaled opex less insurance premium. Prize payouts excluded — carried by the insurer.</t>
         </is>
@@ -4926,7 +4969,7 @@
         <v/>
       </c>
       <c r="F23" s="86" t="n"/>
-      <c r="G23" s="124" t="inlineStr">
+      <c r="G23" s="127" t="inlineStr">
         <is>
           <t>Today solved to the post-money floor; out-years from Assumptions.</t>
         </is>
@@ -4951,7 +4994,7 @@
         <v/>
       </c>
       <c r="F24" s="86" t="n"/>
-      <c r="G24" s="124" t="inlineStr">
+      <c r="G24" s="127" t="inlineStr">
         <is>
           <t>Headline figures from the pitch: R53.3m / R147m / R807m.</t>
         </is>
@@ -4976,7 +5019,7 @@
         <v/>
       </c>
       <c r="F25" s="86" t="n"/>
-      <c r="G25" s="124" t="inlineStr">
+      <c r="G25" s="127" t="inlineStr">
         <is>
           <t>Sanity check: does the ramp x multiple reach the milestone?</t>
         </is>
@@ -5051,7 +5094,7 @@
         <v/>
       </c>
       <c r="F29" s="95" t="n"/>
-      <c r="G29" s="124" t="inlineStr">
+      <c r="G29" s="127" t="inlineStr">
         <is>
           <t>Total revenue in rand. Stream split is rows 9-12 above.</t>
         </is>
@@ -5165,7 +5208,7 @@
       </c>
       <c r="C37" s="126" t="inlineStr">
         <is>
-          <t>Simulator revenue depends on concluding operator agreements, which are not yet signed as at August 2026. Ernie Els holds direct relationships with the target operators; the integration this round funds is what makes Get Lucky ready to sign. Set the attach rate to zero on the Simulator tab to model the group without the stream.</t>
+          <t>Simulator revenue depends on concluding operator agreements, which are not yet signed as at August 2026. Ernie Els holds direct relationships with the target operators, and the integration this round funds is what makes Get Lucky ready to sign. The adoption range on the Simulator tab shows how the 2029 milestone moves with take-up.</t>
         </is>
       </c>
       <c r="D37" s="86" t="n"/>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -1352,12 +1352,12 @@
         </is>
       </c>
       <c r="C26" s="37">
-        <f>350000/Assumptions!$C$11</f>
+        <f>450000/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>Today's monthly opex base (pitch R350k/mo)</t>
+          <t>Funded monthly opex base (R450k/mo) — team, platform and market-entry budget</t>
         </is>
       </c>
     </row>
@@ -1368,11 +1368,11 @@
         </is>
       </c>
       <c r="C27" s="27" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>0.65 ≈ service-inclusive SaaS economies of scale</t>
+          <t>0.68 — costs scale with the base as four streams and four territories come online</t>
         </is>
       </c>
     </row>
@@ -3279,11 +3279,11 @@
         </is>
       </c>
       <c r="C17" s="71" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="E17" s="127" t="inlineStr">
         <is>
-          <t>Software-only channel: no cameras, no installation, no course revenue share. After integration engineering, operator marketing support and platform ops.</t>
+          <t>Software-only channel, but funded to land: integration engineering, operator marketing support and platform operations are carried here.</t>
         </is>
       </c>
     </row>
@@ -4041,11 +4041,11 @@
         </is>
       </c>
       <c r="C22" s="71" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="E22" s="127" t="inlineStr">
         <is>
-          <t>After local activation and partner servicing cost.</t>
+          <t>After local activation, partner servicing and market-entry cost.</t>
         </is>
       </c>
     </row>
@@ -4362,11 +4362,11 @@
         </is>
       </c>
       <c r="C21" s="71" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="I21" s="127" t="inlineStr">
         <is>
-          <t>Sold through the existing checkout: no hardware, no new venue cost.</t>
+          <t>After product build, merchandising and payment costs.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>2.744619</v>
+        <v>2.5</v>
       </c>
       <c r="D30" s="52" t="inlineStr">
         <is>
-          <t>Implied by the published R96.8m base-plan milestone (R96.8m / R35.3m) — not a new assumption</t>
+          <t>Flat revenue multiple — same at every forward milestone</t>
         </is>
       </c>
     </row>
@@ -1420,11 +1420,11 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D31" s="52" t="inlineStr">
         <is>
-          <t>Rated as global &amp; profitable</t>
+          <t>Flat revenue multiple — no expansion assumed at exit</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>147000000/Assumptions!$C$11</f>
+        <f>133877838/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R147m, all revenue streams)</t>
+          <t>Pitch milestone — 3-yr plan (R133.9m at 2.5x revenue)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>807000000/Assumptions!$C$11</f>
+        <f>336424442/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Pitch exit vision (R807m, all revenue streams)</t>
+          <t>Pitch exit vision (R336m at 2.5x revenue)</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
     <row r="31">
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>WHY 6x REVENUE AT EXIT (2032)</t>
+          <t>WHY A FLAT 2.5x REVENUE MULTIPLE</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C35" s="126" t="inlineStr">
         <is>
-          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) have transacted in the 5-10x revenue range at similar scale. 6x sits mid-band.</t>
+          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) trade at 5-10x revenue. This plan applies roughly half the bottom of that band, discounted for being private, pre-scale and mid-execution. Market-anchored, deliberately on the conservative side of it.</t>
         </is>
       </c>
       <c r="D35" s="86" t="n"/>
@@ -5187,12 +5187,12 @@
     <row r="36">
       <c r="B36" s="67" t="inlineStr">
         <is>
-          <t>Risk to the multiple</t>
+          <t>Why flat, not expanding</t>
         </is>
       </c>
       <c r="C36" s="126" t="inlineStr">
         <is>
-          <t>If growth stalls the multiple compresses toward pure SaaS (3-4x), landing 2032 at R404-538m rather than R807m.</t>
+          <t>The same multiple is applied at every forward milestone, so the milestones move only with revenue. The entry multiple is higher (R53.3m post / R11.2m revenue = 4.8x), so the multiple COMPRESSES as the company scales — the direction an investor expects. No multiple expansion is assumed anywhere.</t>
         </is>
       </c>
       <c r="D36" s="86" t="n"/>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D30" s="52" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D31" s="52" t="inlineStr">
         <is>
@@ -1435,12 +1435,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>133877838/Assumptions!$C$11</f>
+        <f>187428972/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R133.9m at 2.5x revenue)</t>
+          <t>Pitch milestone — 3-yr plan (R187.4m at 3.5x revenue)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>336424442/Assumptions!$C$11</f>
+        <f>470994220/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Pitch exit vision (R336m at 2.5x revenue)</t>
+          <t>2032 milestone (R471m at 3.5x revenue)</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
     <row r="31">
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>WHY A FLAT 2.5x REVENUE MULTIPLE</t>
+          <t>WHY A FLAT 3.5x REVENUE MULTIPLE</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C35" s="126" t="inlineStr">
         <is>
-          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) trade at 5-10x revenue. This plan applies roughly half the bottom of that band, discounted for being private, pre-scale and mid-execution. Market-anchored, deliberately on the conservative side of it.</t>
+          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) trade at 5-10x revenue. 3.5x sits 30% below the bottom of that band — a discount for being private and pre-scale, not a stretch.</t>
         </is>
       </c>
       <c r="D35" s="86" t="n"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C36" s="126" t="inlineStr">
         <is>
-          <t>The same multiple is applied at every forward milestone, so the milestones move only with revenue. The entry multiple is higher (R53.3m post / R11.2m revenue = 4.8x), so the multiple COMPRESSES as the company scales — the direction an investor expects. No multiple expansion is assumed anywhere.</t>
+          <t>The same 3.5x is applied at every forward milestone, so the milestones move only with revenue. The entry multiple is higher (R53.3m post / R11.2m revenue = 4.8x), so the multiple COMPRESSES as the company scales. No multiple expansion is assumed anywhere.</t>
         </is>
       </c>
       <c r="D36" s="86" t="n"/>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D30" s="52" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D31" s="52" t="inlineStr">
         <is>
@@ -1435,12 +1435,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>187428972/Assumptions!$C$11</f>
+        <f>160653405/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R187.4m at 3.5x revenue)</t>
+          <t>Pitch milestone — 3-yr plan (R160.7m at 3.0x revenue)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>470994220/Assumptions!$C$11</f>
+        <f>403709331/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>2032 milestone (R471m at 3.5x revenue)</t>
+          <t>2032 milestone (R404m at 3.0x revenue)</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
     <row r="31">
       <c r="B31" s="66" t="inlineStr">
         <is>
-          <t>WHY A FLAT 3.5x REVENUE MULTIPLE</t>
+          <t>WHY A FLAT 3.0x REVENUE MULTIPLE</t>
         </is>
       </c>
       <c r="C31" s="66" t="inlineStr"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C35" s="126" t="inlineStr">
         <is>
-          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) trade at 5-10x revenue. 3.5x sits 30% below the bottom of that band — a discount for being private and pre-scale, not a stretch.</t>
+          <t>Engaged-community subscription businesses (Strava, Peloton, Whoop) trade at 5-10x revenue. 3.0x sits 40% below the bottom of that band — a discount for being private and pre-scale.</t>
         </is>
       </c>
       <c r="D35" s="86" t="n"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C36" s="126" t="inlineStr">
         <is>
-          <t>The same 3.5x is applied at every forward milestone, so the milestones move only with revenue. The entry multiple is higher (R53.3m post / R11.2m revenue = 4.8x), so the multiple COMPRESSES as the company scales. No multiple expansion is assumed anywhere.</t>
+          <t>The same 3.0x is applied at every forward milestone, so the milestones move only with revenue. The entry multiple is higher (R53.3m post / R11.2m revenue = 4.8x), so the multiple COMPRESSES as the company scales. No multiple expansion is assumed anywhere.</t>
         </is>
       </c>
       <c r="D36" s="86" t="n"/>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -40,7 +40,7 @@
     <numFmt numFmtId="178" formatCode="0.0x"/>
     <numFmt numFmtId="179" formatCode="0.00\x"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -250,6 +250,12 @@
       <color rgb="FF335231"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -408,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -620,6 +626,10 @@
     <xf numFmtId="176" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="179" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1435,12 +1445,12 @@
         </is>
       </c>
       <c r="C32" s="36">
-        <f>160653405/Assumptions!$C$11</f>
+        <f>157656339/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Pitch milestone — 3-yr plan (R160.7m at 3.0x revenue)</t>
+          <t>Pitch milestone — 3-yr plan (R157.7m at 3.0x revenue)</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1461,12 @@
         </is>
       </c>
       <c r="C33" s="36">
-        <f>403709331/Assumptions!$C$11</f>
+        <f>396383967/Assumptions!$C$11</f>
         <v/>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>2032 milestone (R404m at 3.0x revenue)</t>
+          <t>2032 milestone (R396m at 3.0x revenue)</t>
         </is>
       </c>
     </row>
@@ -4203,48 +4213,24 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="67" t="inlineStr">
-        <is>
-          <t>Nearest the pin</t>
-        </is>
-      </c>
-      <c r="C11" s="67" t="inlineStr">
-        <is>
-          <t>$3</t>
-        </is>
-      </c>
-      <c r="D11" s="67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" s="126" t="inlineStr">
-        <is>
-          <t>Guaranteed prize inside three feet — monetises the 12,499 shots in 12,500 that are not an ace.</t>
+      <c r="B11" s="131" t="inlineStr">
+        <is>
+          <t>Parked — not in the plan</t>
+        </is>
+      </c>
+      <c r="C11" s="86" t="n"/>
+      <c r="D11" s="86" t="n"/>
+      <c r="E11" s="132" t="inlineStr">
+        <is>
+          <t>Nearest the pin (no way to verify proximity with the current rig) and The highlight reel (no production pipeline yet). Neither is modelled. Both return if and when they can be delivered.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>The highlight reel</t>
-        </is>
-      </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>$3</t>
-        </is>
-      </c>
-      <c r="D12" s="67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E12" s="126" t="inlineStr">
-        <is>
-          <t>The produced clip, scored and branded. No insurance component: pure margin, and every share is marketing.</t>
-        </is>
-      </c>
+      <c r="B12" s="86" t="n"/>
+      <c r="C12" s="86" t="n"/>
+      <c r="D12" s="86" t="n"/>
+      <c r="E12" s="113" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="67" t="inlineStr">
@@ -4287,11 +4273,11 @@
         </is>
       </c>
       <c r="C16" s="71" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="I16" s="127" t="inlineStr">
         <is>
-          <t>Share of subscriber rounds that buy at least one upsell. This golfer already pays ~R200 a swing.</t>
+          <t>Share of subscriber rounds that buy at least one upsell. Cut from 12% when nearest-the-pin and the highlight reel were parked — a shorter menu without the two broadest-appeal items converts fewer buyers.</t>
         </is>
       </c>
     </row>
@@ -4317,11 +4303,11 @@
         </is>
       </c>
       <c r="C18" s="71" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I18" s="127" t="inlineStr">
         <is>
-          <t>Lower: the base simulator entry is $1, so the ask has to be smaller.</t>
+          <t>Cut from 5% for the same reason. The base simulator entry is $1, so the ask has to be smaller.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D48"/>
+  <dimension ref="B2:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -1177,6 +1177,64 @@
         <is>
           <t>48 months from Jan 2026</t>
         </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BLENDED STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Insured swings included in the membership</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>A CAPPED allowance. Unlimited cannot be underwritten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Prize on an included swing ($)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Premium ceded on the membership (% of sub)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Fair price for the included swings at the same target loss ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Get Lucky share of membership</t>
+        </is>
+      </c>
+      <c r="C54">
+        <f>1-C53</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:CH33"/>
+  <dimension ref="B2:CH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -6473,339 +6531,339 @@
         </is>
       </c>
       <c r="C27">
-        <f>C16*Assumptions!$C$19</f>
+        <f>C16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D27">
-        <f>D16*Assumptions!$C$19</f>
+        <f>D16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E27">
-        <f>E16*Assumptions!$C$19</f>
+        <f>E16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F27">
-        <f>F16*Assumptions!$C$19</f>
+        <f>F16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="G27">
-        <f>G16*Assumptions!$C$19</f>
+        <f>G16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H27">
-        <f>H16*Assumptions!$C$19</f>
+        <f>H16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="I27">
-        <f>I16*Assumptions!$C$19</f>
+        <f>I16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="J27">
-        <f>J16*Assumptions!$C$19</f>
+        <f>J16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="K27">
-        <f>K16*Assumptions!$C$19</f>
+        <f>K16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="L27">
-        <f>L16*Assumptions!$C$19</f>
+        <f>L16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="M27">
-        <f>M16*Assumptions!$C$19</f>
+        <f>M16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="N27">
-        <f>N16*Assumptions!$C$19</f>
+        <f>N16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="O27">
-        <f>O16*Assumptions!$C$19</f>
+        <f>O16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="P27">
-        <f>P16*Assumptions!$C$19</f>
+        <f>P16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>Q16*Assumptions!$C$19</f>
+        <f>Q16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="R27">
-        <f>R16*Assumptions!$C$19</f>
+        <f>R16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="S27">
-        <f>S16*Assumptions!$C$19</f>
+        <f>S16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="T27">
-        <f>T16*Assumptions!$C$19</f>
+        <f>T16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="U27">
-        <f>U16*Assumptions!$C$19</f>
+        <f>U16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="V27">
-        <f>V16*Assumptions!$C$19</f>
+        <f>V16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="W27">
-        <f>W16*Assumptions!$C$19</f>
+        <f>W16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="X27">
-        <f>X16*Assumptions!$C$19</f>
+        <f>X16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>Y16*Assumptions!$C$19</f>
+        <f>Y16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="Z27">
-        <f>Z16*Assumptions!$C$19</f>
+        <f>Z16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>AA16*Assumptions!$C$19</f>
+        <f>AA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>AB16*Assumptions!$C$19</f>
+        <f>AB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>AC16*Assumptions!$C$19</f>
+        <f>AC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>AD16*Assumptions!$C$19</f>
+        <f>AD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>AE16*Assumptions!$C$19</f>
+        <f>AE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AF27">
-        <f>AF16*Assumptions!$C$19</f>
+        <f>AF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AG27">
-        <f>AG16*Assumptions!$C$19</f>
+        <f>AG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AH27">
-        <f>AH16*Assumptions!$C$19</f>
+        <f>AH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AI27">
-        <f>AI16*Assumptions!$C$19</f>
+        <f>AI16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AJ27">
-        <f>AJ16*Assumptions!$C$19</f>
+        <f>AJ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AK27">
-        <f>AK16*Assumptions!$C$19</f>
+        <f>AK16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AL27">
-        <f>AL16*Assumptions!$C$19</f>
+        <f>AL16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AM27">
-        <f>AM16*Assumptions!$C$19</f>
+        <f>AM16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AN27">
-        <f>AN16*Assumptions!$C$19</f>
+        <f>AN16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AO27">
-        <f>AO16*Assumptions!$C$19</f>
+        <f>AO16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AP27">
-        <f>AP16*Assumptions!$C$19</f>
+        <f>AP16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AQ27">
-        <f>AQ16*Assumptions!$C$19</f>
+        <f>AQ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AR27">
-        <f>AR16*Assumptions!$C$19</f>
+        <f>AR16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AS27">
-        <f>AS16*Assumptions!$C$19</f>
+        <f>AS16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AT27">
-        <f>AT16*Assumptions!$C$19</f>
+        <f>AT16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AU27">
-        <f>AU16*Assumptions!$C$19</f>
+        <f>AU16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AV27">
-        <f>AV16*Assumptions!$C$19</f>
+        <f>AV16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AW27">
-        <f>AW16*Assumptions!$C$19</f>
+        <f>AW16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AX27">
-        <f>AX16*Assumptions!$C$19</f>
+        <f>AX16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AY27">
-        <f>AY16*Assumptions!$C$19</f>
+        <f>AY16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="AZ27">
-        <f>AZ16*Assumptions!$C$19</f>
+        <f>AZ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BA27">
-        <f>BA16*Assumptions!$C$19</f>
+        <f>BA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BB27">
-        <f>BB16*Assumptions!$C$19</f>
+        <f>BB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BC27">
-        <f>BC16*Assumptions!$C$19</f>
+        <f>BC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BD27">
-        <f>BD16*Assumptions!$C$19</f>
+        <f>BD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BE27">
-        <f>BE16*Assumptions!$C$19</f>
+        <f>BE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BF27">
-        <f>BF16*Assumptions!$C$19</f>
+        <f>BF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BG27">
-        <f>BG16*Assumptions!$C$19</f>
+        <f>BG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BH27">
-        <f>BH16*Assumptions!$C$19</f>
+        <f>BH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BI27">
-        <f>BI16*Assumptions!$C$19</f>
+        <f>BI16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BJ27">
-        <f>BJ16*Assumptions!$C$19</f>
+        <f>BJ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BK27">
-        <f>BK16*Assumptions!$C$19</f>
+        <f>BK16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BL27">
-        <f>BL16*Assumptions!$C$19</f>
+        <f>BL16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BM27">
-        <f>BM16*Assumptions!$C$19</f>
+        <f>BM16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BN27">
-        <f>BN16*Assumptions!$C$19</f>
+        <f>BN16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BO27">
-        <f>BO16*Assumptions!$C$19</f>
+        <f>BO16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BP27">
-        <f>BP16*Assumptions!$C$19</f>
+        <f>BP16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BQ27">
-        <f>BQ16*Assumptions!$C$19</f>
+        <f>BQ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BR27">
-        <f>BR16*Assumptions!$C$19</f>
+        <f>BR16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BS27">
-        <f>BS16*Assumptions!$C$19</f>
+        <f>BS16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BT27">
-        <f>BT16*Assumptions!$C$19</f>
+        <f>BT16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BU27">
-        <f>BU16*Assumptions!$C$19</f>
+        <f>BU16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BV27">
-        <f>BV16*Assumptions!$C$19</f>
+        <f>BV16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BW27">
-        <f>BW16*Assumptions!$C$19</f>
+        <f>BW16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BX27">
-        <f>BX16*Assumptions!$C$19</f>
+        <f>BX16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BY27">
-        <f>BY16*Assumptions!$C$19</f>
+        <f>BY16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="BZ27">
-        <f>BZ16*Assumptions!$C$19</f>
+        <f>BZ16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CA27">
-        <f>CA16*Assumptions!$C$19</f>
+        <f>CA16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CB27">
-        <f>CB16*Assumptions!$C$19</f>
+        <f>CB16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CC27">
-        <f>CC16*Assumptions!$C$19</f>
+        <f>CC16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CD27">
-        <f>CD16*Assumptions!$C$19</f>
+        <f>CD16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CE27">
-        <f>CE16*Assumptions!$C$19</f>
+        <f>CE16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CF27">
-        <f>CF16*Assumptions!$C$19</f>
+        <f>CF16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CG27">
-        <f>CG16*Assumptions!$C$19</f>
+        <f>CG16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="CH27">
-        <f>CH16*Assumptions!$C$19</f>
+        <f>CH16*Assumptions!$C$19*Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -7495,6 +7553,349 @@
         <v/>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Membership premium ceded ($)</t>
+        </is>
+      </c>
+      <c r="C30">
+        <f>C16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="D30">
+        <f>D16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>E16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="F30">
+        <f>F16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>G16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>H16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>I16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="J30">
+        <f>J16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>K16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>L16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>M16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="N30">
+        <f>N16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="O30">
+        <f>O16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="P30">
+        <f>P16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Q30">
+        <f>Q16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="R30">
+        <f>R16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="S30">
+        <f>S16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>T16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="U30">
+        <f>U16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="V30">
+        <f>V16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="W30">
+        <f>W16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>X16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>Y16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>Z16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>AA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>AB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>AC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>AD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>AE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AF30">
+        <f>AF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AG30">
+        <f>AG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AH30">
+        <f>AH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AI30">
+        <f>AI16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AJ30">
+        <f>AJ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AK30">
+        <f>AK16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AL30">
+        <f>AL16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AM30">
+        <f>AM16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AN30">
+        <f>AN16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AO30">
+        <f>AO16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AP30">
+        <f>AP16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AQ30">
+        <f>AQ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AR30">
+        <f>AR16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AS30">
+        <f>AS16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AT30">
+        <f>AT16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AU30">
+        <f>AU16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AV30">
+        <f>AV16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AW30">
+        <f>AW16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AX30">
+        <f>AX16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AY30">
+        <f>AY16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="AZ30">
+        <f>AZ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BA30">
+        <f>BA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BB30">
+        <f>BB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BC30">
+        <f>BC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BD30">
+        <f>BD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BE30">
+        <f>BE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BF30">
+        <f>BF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BG30">
+        <f>BG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BH30">
+        <f>BH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BI30">
+        <f>BI16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BJ30">
+        <f>BJ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BK30">
+        <f>BK16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BL30">
+        <f>BL16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BM30">
+        <f>BM16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BN30">
+        <f>BN16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BO30">
+        <f>BO16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BP30">
+        <f>BP16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BQ30">
+        <f>BQ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BR30">
+        <f>BR16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BS30">
+        <f>BS16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BT30">
+        <f>BT16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BU30">
+        <f>BU16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BV30">
+        <f>BV16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BW30">
+        <f>BW16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BX30">
+        <f>BX16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BY30">
+        <f>BY16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="BZ30">
+        <f>BZ16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CA30">
+        <f>CA16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CB30">
+        <f>CB16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CC30">
+        <f>CC16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CD30">
+        <f>CD16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CE30">
+        <f>CE16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CF30">
+        <f>CF16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CG30">
+        <f>CG16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="CH30">
+        <f>CH16*Assumptions!$C$19*Assumptions!$C$53</f>
+        <v/>
+      </c>
+    </row>
     <row r="31">
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -7852,339 +8253,682 @@
         </is>
       </c>
       <c r="C33">
-        <f>C20*Insurance!$C$28</f>
+        <f>C20*Insurance!$C$28+C34</f>
         <v/>
       </c>
       <c r="D33">
-        <f>D20*Insurance!$C$28</f>
+        <f>D20*Insurance!$C$28+D34</f>
         <v/>
       </c>
       <c r="E33">
-        <f>E20*Insurance!$C$28</f>
+        <f>E20*Insurance!$C$28+E34</f>
         <v/>
       </c>
       <c r="F33">
-        <f>F20*Insurance!$C$28</f>
+        <f>F20*Insurance!$C$28+F34</f>
         <v/>
       </c>
       <c r="G33">
-        <f>G20*Insurance!$C$28</f>
+        <f>G20*Insurance!$C$28+G34</f>
         <v/>
       </c>
       <c r="H33">
-        <f>H20*Insurance!$C$28</f>
+        <f>H20*Insurance!$C$28+H34</f>
         <v/>
       </c>
       <c r="I33">
-        <f>I20*Insurance!$C$28</f>
+        <f>I20*Insurance!$C$28+I34</f>
         <v/>
       </c>
       <c r="J33">
-        <f>J20*Insurance!$C$28</f>
+        <f>J20*Insurance!$C$28+J34</f>
         <v/>
       </c>
       <c r="K33">
-        <f>K20*Insurance!$C$28</f>
+        <f>K20*Insurance!$C$28+K34</f>
         <v/>
       </c>
       <c r="L33">
-        <f>L20*Insurance!$C$28</f>
+        <f>L20*Insurance!$C$28+L34</f>
         <v/>
       </c>
       <c r="M33">
-        <f>M20*Insurance!$C$28</f>
+        <f>M20*Insurance!$C$28+M34</f>
         <v/>
       </c>
       <c r="N33">
-        <f>N20*Insurance!$C$28</f>
+        <f>N20*Insurance!$C$28+N34</f>
         <v/>
       </c>
       <c r="O33">
-        <f>O20*Insurance!$C$28</f>
+        <f>O20*Insurance!$C$28+O34</f>
         <v/>
       </c>
       <c r="P33">
-        <f>P20*Insurance!$C$28</f>
+        <f>P20*Insurance!$C$28+P34</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>Q20*Insurance!$C$28</f>
+        <f>Q20*Insurance!$C$28+Q34</f>
         <v/>
       </c>
       <c r="R33">
-        <f>R20*Insurance!$C$28</f>
+        <f>R20*Insurance!$C$28+R34</f>
         <v/>
       </c>
       <c r="S33">
-        <f>S20*Insurance!$C$28</f>
+        <f>S20*Insurance!$C$28+S34</f>
         <v/>
       </c>
       <c r="T33">
-        <f>T20*Insurance!$C$28</f>
+        <f>T20*Insurance!$C$28+T34</f>
         <v/>
       </c>
       <c r="U33">
-        <f>U20*Insurance!$C$28</f>
+        <f>U20*Insurance!$C$28+U34</f>
         <v/>
       </c>
       <c r="V33">
-        <f>V20*Insurance!$C$28</f>
+        <f>V20*Insurance!$C$28+V34</f>
         <v/>
       </c>
       <c r="W33">
-        <f>W20*Insurance!$C$28</f>
+        <f>W20*Insurance!$C$28+W34</f>
         <v/>
       </c>
       <c r="X33">
-        <f>X20*Insurance!$C$28</f>
+        <f>X20*Insurance!$C$28+X34</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>Y20*Insurance!$C$28</f>
+        <f>Y20*Insurance!$C$28+Y34</f>
         <v/>
       </c>
       <c r="Z33">
-        <f>Z20*Insurance!$C$28</f>
+        <f>Z20*Insurance!$C$28+Z34</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>AA20*Insurance!$C$28</f>
+        <f>AA20*Insurance!$C$28+AA34</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>AB20*Insurance!$C$28</f>
+        <f>AB20*Insurance!$C$28+AB34</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>AC20*Insurance!$C$28</f>
+        <f>AC20*Insurance!$C$28+AC34</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>AD20*Insurance!$C$28</f>
+        <f>AD20*Insurance!$C$28+AD34</f>
         <v/>
       </c>
       <c r="AE33">
-        <f>AE20*Insurance!$C$28</f>
+        <f>AE20*Insurance!$C$28+AE34</f>
         <v/>
       </c>
       <c r="AF33">
-        <f>AF20*Insurance!$C$28</f>
+        <f>AF20*Insurance!$C$28+AF34</f>
         <v/>
       </c>
       <c r="AG33">
-        <f>AG20*Insurance!$C$28</f>
+        <f>AG20*Insurance!$C$28+AG34</f>
         <v/>
       </c>
       <c r="AH33">
-        <f>AH20*Insurance!$C$28</f>
+        <f>AH20*Insurance!$C$28+AH34</f>
         <v/>
       </c>
       <c r="AI33">
-        <f>AI20*Insurance!$C$28</f>
+        <f>AI20*Insurance!$C$28+AI34</f>
         <v/>
       </c>
       <c r="AJ33">
-        <f>AJ20*Insurance!$C$28</f>
+        <f>AJ20*Insurance!$C$28+AJ34</f>
         <v/>
       </c>
       <c r="AK33">
-        <f>AK20*Insurance!$C$28</f>
+        <f>AK20*Insurance!$C$28+AK34</f>
         <v/>
       </c>
       <c r="AL33">
-        <f>AL20*Insurance!$C$28</f>
+        <f>AL20*Insurance!$C$28+AL34</f>
         <v/>
       </c>
       <c r="AM33">
-        <f>AM20*Insurance!$C$28</f>
+        <f>AM20*Insurance!$C$28+AM34</f>
         <v/>
       </c>
       <c r="AN33">
-        <f>AN20*Insurance!$C$28</f>
+        <f>AN20*Insurance!$C$28+AN34</f>
         <v/>
       </c>
       <c r="AO33">
-        <f>AO20*Insurance!$C$28</f>
+        <f>AO20*Insurance!$C$28+AO34</f>
         <v/>
       </c>
       <c r="AP33">
-        <f>AP20*Insurance!$C$28</f>
+        <f>AP20*Insurance!$C$28+AP34</f>
         <v/>
       </c>
       <c r="AQ33">
-        <f>AQ20*Insurance!$C$28</f>
+        <f>AQ20*Insurance!$C$28+AQ34</f>
         <v/>
       </c>
       <c r="AR33">
-        <f>AR20*Insurance!$C$28</f>
+        <f>AR20*Insurance!$C$28+AR34</f>
         <v/>
       </c>
       <c r="AS33">
-        <f>AS20*Insurance!$C$28</f>
+        <f>AS20*Insurance!$C$28+AS34</f>
         <v/>
       </c>
       <c r="AT33">
-        <f>AT20*Insurance!$C$28</f>
+        <f>AT20*Insurance!$C$28+AT34</f>
         <v/>
       </c>
       <c r="AU33">
-        <f>AU20*Insurance!$C$28</f>
+        <f>AU20*Insurance!$C$28+AU34</f>
         <v/>
       </c>
       <c r="AV33">
-        <f>AV20*Insurance!$C$28</f>
+        <f>AV20*Insurance!$C$28+AV34</f>
         <v/>
       </c>
       <c r="AW33">
-        <f>AW20*Insurance!$C$28</f>
+        <f>AW20*Insurance!$C$28+AW34</f>
         <v/>
       </c>
       <c r="AX33">
-        <f>AX20*Insurance!$C$28</f>
+        <f>AX20*Insurance!$C$28+AX34</f>
         <v/>
       </c>
       <c r="AY33">
-        <f>AY20*Insurance!$C$28</f>
+        <f>AY20*Insurance!$C$28+AY34</f>
         <v/>
       </c>
       <c r="AZ33">
-        <f>AZ20*Insurance!$C$28</f>
+        <f>AZ20*Insurance!$C$28+AZ34</f>
         <v/>
       </c>
       <c r="BA33">
-        <f>BA20*Insurance!$C$28</f>
+        <f>BA20*Insurance!$C$28+BA34</f>
         <v/>
       </c>
       <c r="BB33">
-        <f>BB20*Insurance!$C$28</f>
+        <f>BB20*Insurance!$C$28+BB34</f>
         <v/>
       </c>
       <c r="BC33">
-        <f>BC20*Insurance!$C$28</f>
+        <f>BC20*Insurance!$C$28+BC34</f>
         <v/>
       </c>
       <c r="BD33">
-        <f>BD20*Insurance!$C$28</f>
+        <f>BD20*Insurance!$C$28+BD34</f>
         <v/>
       </c>
       <c r="BE33">
-        <f>BE20*Insurance!$C$28</f>
+        <f>BE20*Insurance!$C$28+BE34</f>
         <v/>
       </c>
       <c r="BF33">
-        <f>BF20*Insurance!$C$28</f>
+        <f>BF20*Insurance!$C$28+BF34</f>
         <v/>
       </c>
       <c r="BG33">
-        <f>BG20*Insurance!$C$28</f>
+        <f>BG20*Insurance!$C$28+BG34</f>
         <v/>
       </c>
       <c r="BH33">
-        <f>BH20*Insurance!$C$28</f>
+        <f>BH20*Insurance!$C$28+BH34</f>
         <v/>
       </c>
       <c r="BI33">
-        <f>BI20*Insurance!$C$28</f>
+        <f>BI20*Insurance!$C$28+BI34</f>
         <v/>
       </c>
       <c r="BJ33">
-        <f>BJ20*Insurance!$C$28</f>
+        <f>BJ20*Insurance!$C$28+BJ34</f>
         <v/>
       </c>
       <c r="BK33">
-        <f>BK20*Insurance!$C$28</f>
+        <f>BK20*Insurance!$C$28+BK34</f>
         <v/>
       </c>
       <c r="BL33">
-        <f>BL20*Insurance!$C$28</f>
+        <f>BL20*Insurance!$C$28+BL34</f>
         <v/>
       </c>
       <c r="BM33">
-        <f>BM20*Insurance!$C$28</f>
+        <f>BM20*Insurance!$C$28+BM34</f>
         <v/>
       </c>
       <c r="BN33">
-        <f>BN20*Insurance!$C$28</f>
+        <f>BN20*Insurance!$C$28+BN34</f>
         <v/>
       </c>
       <c r="BO33">
-        <f>BO20*Insurance!$C$28</f>
+        <f>BO20*Insurance!$C$28+BO34</f>
         <v/>
       </c>
       <c r="BP33">
-        <f>BP20*Insurance!$C$28</f>
+        <f>BP20*Insurance!$C$28+BP34</f>
         <v/>
       </c>
       <c r="BQ33">
-        <f>BQ20*Insurance!$C$28</f>
+        <f>BQ20*Insurance!$C$28+BQ34</f>
         <v/>
       </c>
       <c r="BR33">
-        <f>BR20*Insurance!$C$28</f>
+        <f>BR20*Insurance!$C$28+BR34</f>
         <v/>
       </c>
       <c r="BS33">
-        <f>BS20*Insurance!$C$28</f>
+        <f>BS20*Insurance!$C$28+BS34</f>
         <v/>
       </c>
       <c r="BT33">
-        <f>BT20*Insurance!$C$28</f>
+        <f>BT20*Insurance!$C$28+BT34</f>
         <v/>
       </c>
       <c r="BU33">
-        <f>BU20*Insurance!$C$28</f>
+        <f>BU20*Insurance!$C$28+BU34</f>
         <v/>
       </c>
       <c r="BV33">
-        <f>BV20*Insurance!$C$28</f>
+        <f>BV20*Insurance!$C$28+BV34</f>
         <v/>
       </c>
       <c r="BW33">
-        <f>BW20*Insurance!$C$28</f>
+        <f>BW20*Insurance!$C$28+BW34</f>
         <v/>
       </c>
       <c r="BX33">
-        <f>BX20*Insurance!$C$28</f>
+        <f>BX20*Insurance!$C$28+BX34</f>
         <v/>
       </c>
       <c r="BY33">
-        <f>BY20*Insurance!$C$28</f>
+        <f>BY20*Insurance!$C$28+BY34</f>
         <v/>
       </c>
       <c r="BZ33">
-        <f>BZ20*Insurance!$C$28</f>
+        <f>BZ20*Insurance!$C$28+BZ34</f>
         <v/>
       </c>
       <c r="CA33">
-        <f>CA20*Insurance!$C$28</f>
+        <f>CA20*Insurance!$C$28+CA34</f>
         <v/>
       </c>
       <c r="CB33">
-        <f>CB20*Insurance!$C$28</f>
+        <f>CB20*Insurance!$C$28+CB34</f>
         <v/>
       </c>
       <c r="CC33">
-        <f>CC20*Insurance!$C$28</f>
+        <f>CC20*Insurance!$C$28+CC34</f>
         <v/>
       </c>
       <c r="CD33">
-        <f>CD20*Insurance!$C$28</f>
+        <f>CD20*Insurance!$C$28+CD34</f>
         <v/>
       </c>
       <c r="CE33">
-        <f>CE20*Insurance!$C$28</f>
+        <f>CE20*Insurance!$C$28+CE34</f>
         <v/>
       </c>
       <c r="CF33">
-        <f>CF20*Insurance!$C$28</f>
+        <f>CF20*Insurance!$C$28+CF34</f>
         <v/>
       </c>
       <c r="CG33">
-        <f>CG20*Insurance!$C$28</f>
+        <f>CG20*Insurance!$C$28+CG34</f>
         <v/>
       </c>
       <c r="CH33">
-        <f>CH20*Insurance!$C$28</f>
+        <f>CH20*Insurance!$C$28+CH34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Claims on included swings ($)</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>C16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>D16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>E16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>F16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>G16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>H16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>I16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>J16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>K16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>L16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>M16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="N34">
+        <f>N16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="O34">
+        <f>O16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="P34">
+        <f>P16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Q34">
+        <f>Q16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>R16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>S16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="T34">
+        <f>T16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="U34">
+        <f>U16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="V34">
+        <f>V16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="W34">
+        <f>W16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>X16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>Y16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="Z34">
+        <f>Z16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>AA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>AB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>AC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>AD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>AE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AF34">
+        <f>AF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AG34">
+        <f>AG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AH34">
+        <f>AH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AI34">
+        <f>AI16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AJ34">
+        <f>AJ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AK34">
+        <f>AK16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AL34">
+        <f>AL16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AM34">
+        <f>AM16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AN34">
+        <f>AN16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AO34">
+        <f>AO16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AP34">
+        <f>AP16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AQ34">
+        <f>AQ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AR34">
+        <f>AR16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AS34">
+        <f>AS16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AT34">
+        <f>AT16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AU34">
+        <f>AU16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AV34">
+        <f>AV16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AW34">
+        <f>AW16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AX34">
+        <f>AX16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AY34">
+        <f>AY16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="AZ34">
+        <f>AZ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BA34">
+        <f>BA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BB34">
+        <f>BB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BC34">
+        <f>BC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BD34">
+        <f>BD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BE34">
+        <f>BE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BF34">
+        <f>BF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BG34">
+        <f>BG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BH34">
+        <f>BH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BI34">
+        <f>BI16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BJ34">
+        <f>BJ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BK34">
+        <f>BK16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BL34">
+        <f>BL16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BM34">
+        <f>BM16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BN34">
+        <f>BN16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BO34">
+        <f>BO16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BP34">
+        <f>BP16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BQ34">
+        <f>BQ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BR34">
+        <f>BR16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BS34">
+        <f>BS16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BT34">
+        <f>BT16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BU34">
+        <f>BU16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BV34">
+        <f>BV16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BW34">
+        <f>BW16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BX34">
+        <f>BX16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BY34">
+        <f>BY16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="BZ34">
+        <f>BZ16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CA34">
+        <f>CA16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CB34">
+        <f>CB16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CC34">
+        <f>CC16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CD34">
+        <f>CD16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CE34">
+        <f>CE16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CF34">
+        <f>CF16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CG34">
+        <f>CG16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
+        <v/>
+      </c>
+      <c r="CH34">
+        <f>CH16*Assumptions!$C$51*Assumptions!$C$52*Insurance!$C$8</f>
         <v/>
       </c>
     </row>
@@ -8199,7 +8943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H28"/>
+  <dimension ref="B2:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -8558,6 +9302,86 @@
       <c r="C28">
         <f>G18</f>
         <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>BLENDED — per member per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Included swings expected claim ($)</t>
+        </is>
+      </c>
+      <c r="C31">
+        <f>Assumptions!C51*Assumptions!C52*C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Premium ceded on membership ($)</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>Assumptions!C19*Assumptions!C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Trade-up premium ($)</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Trade-up expected claim ($)</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Blended loss ratio</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>(C31+C34)/(C32+C33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Counterfactual — 16 swings/mo at $10,000, unlimited</t>
+        </is>
+      </c>
+      <c r="C36">
+        <f>16*10000*C8/(Assumptions!C19*0.24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>A 533% loss ratio. This is why unlimited cannot be written.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8901,31 +9725,31 @@
         </is>
       </c>
       <c r="C18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="D18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="E18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="F18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="G18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="H18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="I18">
-        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$27:$CH$27)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
+        <f>((SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$27:$CH$27)/Assumptions!$C$54)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$21:$CH$21)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$20:$CH$20)*Assumptions!$C$33*Assumptions!$C$34)*Assumptions!$C$6*Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -9310,35 +10134,35 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Premium ceded (24%)</t>
+          <t>Premium ceded (membership + entries)</t>
         </is>
       </c>
       <c r="C34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,C$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="D34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,D$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="E34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,E$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="F34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,F$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="G34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,G$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="H34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,H$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
       <c r="I34">
-        <f>SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$22:$CH$22)*Assumptions!$C$6</f>
+        <f>(SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$22:$CH$22)+SUMIF('Build (Monthly)'!$C$6:$CH$6,I$5,'Build (Monthly)'!$C$30:$CH$30))*Assumptions!$C$6</f>
         <v/>
       </c>
     </row>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D60"/>
+  <dimension ref="B2:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -715,11 +715,11 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.169</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>16.9% — repriced 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -1289,6 +1289,21 @@
       <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Realised across 10,000 trailing entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Simulator delivery cost (% of simulator revenue)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Integration engineering, operator marketing support, platform ops</t>
         </is>
       </c>
     </row>
@@ -8592,19 +8607,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2399820</v>
       </c>
       <c r="D13" t="n">
-        <v>2399820</v>
+        <v>6399520</v>
       </c>
       <c r="E13" t="n">
-        <v>6399520</v>
+        <v>11999100</v>
       </c>
       <c r="F13" t="n">
-        <v>11999100</v>
+        <v>16663000</v>
       </c>
       <c r="G13" t="n">
-        <v>20000000</v>
+        <v>23142000</v>
       </c>
       <c r="H13" t="n">
         <v>31997600</v>
@@ -8844,13 +8859,13 @@
         <v>24000000</v>
       </c>
       <c r="F22" t="n">
-        <v>32000000</v>
+        <v>30000000</v>
       </c>
       <c r="G22" t="n">
-        <v>42000000</v>
+        <v>37000000</v>
       </c>
       <c r="H22" t="n">
-        <v>55000000</v>
+        <v>46000000</v>
       </c>
     </row>
     <row r="23">
@@ -8860,27 +8875,58 @@
         </is>
       </c>
       <c r="C23">
-        <f>SUM(C18:C22)</f>
+        <f>SUM(C18:C22)+C24</f>
         <v/>
       </c>
       <c r="D23">
-        <f>SUM(D18:D22)</f>
+        <f>SUM(D18:D22)+D24</f>
         <v/>
       </c>
       <c r="E23">
-        <f>SUM(E18:E22)</f>
+        <f>SUM(E18:E22)+E24</f>
         <v/>
       </c>
       <c r="F23">
-        <f>SUM(F18:F22)</f>
+        <f>SUM(F18:F22)+F24</f>
         <v/>
       </c>
       <c r="G23">
-        <f>SUM(G18:G22)</f>
+        <f>SUM(G18:G22)+G24</f>
         <v/>
       </c>
       <c r="H23">
-        <f>SUM(H18:H22)</f>
+        <f>SUM(H18:H22)+H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Simulator delivery</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>C13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>D13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>E13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>F13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>G13*Assumptions!$C$61</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>H13*Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -9422,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R53.3m / R113.1m (Dec 2029) / R288.9m (2032).</t>
+          <t>Headline figures from the pitch: R47.3m / R129.9m (Dec 2029) / R288.9m (2032).</t>
         </is>
       </c>
     </row>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -704,38 +704,38 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>This round</t>
+          <t>Raise</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equity offered</t>
+          <t>Pre-money valuation (ZAR)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.169</v>
+        <v>39000000</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>16.9% — repriced 2026-08-05</t>
+          <t>R39m pre — the round is quoted on pre-money</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Post-money (ZAR)</t>
+          <t>Post-money valuation (ZAR)</t>
         </is>
       </c>
       <c r="C9">
-        <f>C7/C8</f>
+        <f>C8+C7</f>
         <v/>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Exact: 8.0m / 15%</t>
+          <t>R47m post; equity = 8/47 = 17.0%</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="2" max="2"/>
@@ -9361,7 +9361,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stake</t>
+          <t>Stake (raise / post-money)</t>
         </is>
       </c>
       <c r="C14">
@@ -9468,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R47.3m / R129.9m (Dec 2029) / R288.9m (2032).</t>
+          <t>Headline figures from the pitch: R47m / R130m (Dec 2029) / R289m (2032).</t>
         </is>
       </c>
     </row>
@@ -9512,6 +9512,58 @@
         <is>
           <t>Insurance terms are a submission, not a bound policy.</t>
         </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MULTIPLE SENSITIVITY — the 3.0x is a choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>At 2.5x</t>
+        </is>
+      </c>
+      <c r="C32">
+        <f>Annual!E15*2.5</f>
+        <v/>
+      </c>
+      <c r="D32">
+        <f>C32*$C$14/$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>At 3.0x (used)</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>Annual!E15*3</f>
+        <v/>
+      </c>
+      <c r="D33">
+        <f>C33*$C$14/$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>At 3.5x</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>Annual!E15*3.5</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>C34*$C$14/$C$13</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -711,15 +711,15 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pre-money valuation (ZAR)</t>
+          <t>Equity offered</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>39000000</v>
+        <v>0.15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R39m pre — the round is quoted on pre-money</t>
+          <t>15% — the founder's fixed term</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
         </is>
       </c>
       <c r="C9">
-        <f>C8+C7</f>
+        <f>C7/C8</f>
         <v/>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R47m post; equity = 8/47 = 17.0%</t>
+          <t>R53.3m post; pre-money R45.3m</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headline figures from the pitch: R47m / R130m (Dec 2029) / R289m (2032).</t>
+          <t>Headline figures from the pitch: R53.3m / R130m (Dec 2029) / R289m (2032).</t>
         </is>
       </c>
     </row>

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -470,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -541,7 +540,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
@@ -556,7 +554,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -585,7 +582,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
@@ -600,7 +596,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
@@ -608,7 +603,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
@@ -765,11 +759,11 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Includes the invite loop: every slip seats three guests</t>
+          <t>Aggressive build — invite loop + paid marketing; founder-set 100k subscribers by 2032</t>
         </is>
       </c>
     </row>
@@ -780,7 +774,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.095</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="16">
@@ -790,7 +784,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="17">
@@ -800,7 +794,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.073</v>
+        <v>0.109</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -1083,11 +1077,11 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Invited seats are free acquisition</t>
+          <t>CAC per gross new organizer</t>
         </is>
       </c>
     </row>
@@ -1098,11 +1092,11 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>A global consumer app spends real money on brand</t>
+          <t>A global consumer build spends hard on brand</t>
         </is>
       </c>
     </row>
@@ -7069,22 +7063,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9500000</v>
+        <v>11000000</v>
       </c>
       <c r="D24" t="n">
-        <v>16000000</v>
+        <v>18000000</v>
       </c>
       <c r="E24" t="n">
-        <v>25000000</v>
+        <v>28000000</v>
       </c>
       <c r="F24" t="n">
-        <v>33000000</v>
+        <v>42000000</v>
       </c>
       <c r="G24" t="n">
-        <v>42000000</v>
+        <v>62000000</v>
       </c>
       <c r="H24" t="n">
-        <v>53000000</v>
+        <v>88000000</v>
       </c>
     </row>
     <row r="25">
@@ -7187,22 +7181,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3500000</v>
+        <v>4400000</v>
       </c>
       <c r="D30" t="n">
-        <v>2800000</v>
+        <v>3200000</v>
       </c>
       <c r="E30" t="n">
-        <v>2200000</v>
+        <v>2500000</v>
       </c>
       <c r="F30" t="n">
-        <v>1900000</v>
+        <v>2500000</v>
       </c>
       <c r="G30" t="n">
-        <v>1700000</v>
+        <v>2500000</v>
       </c>
       <c r="H30" t="n">
-        <v>1500000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="31">
@@ -7766,7 +7760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E34"/>
+  <dimension ref="B2:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -7998,6 +7992,11 @@
           <t>MULTIPLE SENSITIVITY — 3.0x is a choice</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Headline figures from the pitch: R53.3m / R185.0m (Dec 2029) / R967.8m (2032).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="170" formatCode="$0.00"/>
     <numFmt numFmtId="171" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -191,6 +191,12 @@
       <color rgb="009A937B"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009A937B"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -241,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -325,6 +331,8 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -608,7 +616,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cumulative cash (ZAR) — peak drawdown inside the raise</a:t>
+              <a:t>Cumulative cash (ZAR) — trough inside the raise</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -707,9 +715,6 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="345230"/>
-            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -749,12 +754,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Dashboard'!$O$48:$O$50</f>
+              <f>'Dashboard'!$B$95:$B$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$P$48:$P$50</f>
+              <f>'Dashboard'!$C$95:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -878,12 +883,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Dashboard'!$O$41:$O$45</f>
+              <f>'Dashboard'!$B$89:$B$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$P$41:$P$45</f>
+              <f>'Dashboard'!$C$89:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -891,7 +896,7 @@
       </pieChart>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -903,12 +908,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5580000" cy="3024000"/>
+    <ext cx="5400000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -925,12 +930,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5580000" cy="3024000"/>
+    <ext cx="5400000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -947,12 +952,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3384000" cy="2736000"/>
+    <ext cx="5400000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -969,12 +974,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2376000" cy="2736000"/>
+    <ext cx="5400000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1497,24 +1502,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:P51"/>
+  <dimension ref="B2:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
-    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1534,7 +1532,7 @@
     <row r="5">
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Revenue 2029</t>
+          <t>REVENUE 2029</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1544,20 +1542,20 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Milestone Dec 2029</t>
+          <t>MILESTONE DEC 2029</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="55">
+      <c r="B6" s="77">
         <f>Annual!E17</f>
         <v/>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="77">
         <f>Annual!E27</f>
         <v/>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="77">
         <f>Valuation!D10</f>
         <v/>
       </c>
@@ -1565,17 +1563,17 @@
     <row r="8">
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Investor multiple 2029</t>
+          <t>INVESTOR MULTIPLE 2029</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Peak drawdown</t>
+          <t>PEAK DRAWDOWN</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Subscribers 2032</t>
+          <t>SUBSCRIBERS 2032</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1582,7 @@
         <f>Valuation!D16</f>
         <v/>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="77">
         <f>Valuation!C21</f>
         <v/>
       </c>
@@ -2098,112 +2096,95 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="O40" s="26" t="inlineStr">
-        <is>
-          <t>USE OF FUNDS (helper — chart data)</t>
-        </is>
-      </c>
-      <c r="P40" s="26" t="n"/>
-    </row>
-    <row r="41">
-      <c r="O41" s="26" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="78" t="inlineStr">
+        <is>
+          <t>CHART DATA (calculated — do not edit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="26" t="inlineStr">
         <is>
           <t>App build</t>
         </is>
       </c>
-      <c r="P41" s="26" t="n">
+      <c r="C89" s="26" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="42">
-      <c r="O42" s="26" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="26" t="inlineStr">
         <is>
           <t>Ops &amp; Team</t>
         </is>
       </c>
-      <c r="P42" s="26" t="n">
+      <c r="C90" s="26" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="43">
-      <c r="O43" s="26" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="26" t="inlineStr">
         <is>
           <t>Market &amp; brand</t>
         </is>
       </c>
-      <c r="P43" s="26" t="n">
+      <c r="C91" s="26" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="44">
-      <c r="O44" s="26" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="26" t="inlineStr">
         <is>
           <t>Simulators</t>
         </is>
       </c>
-      <c r="P44" s="26" t="n">
+      <c r="C92" s="26" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="45">
-      <c r="O45" s="26" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="P45" s="26" t="n">
+      <c r="C93" s="26" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="46">
-      <c r="O46" s="26" t="n"/>
-      <c r="P46" s="26" t="n"/>
-    </row>
-    <row r="47">
-      <c r="O47" s="26" t="inlineStr">
-        <is>
-          <t>MILESTONES (helper — chart data)</t>
-        </is>
-      </c>
-      <c r="P47" s="26" t="n"/>
-    </row>
-    <row r="48">
-      <c r="O48" s="26" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="26" t="inlineStr">
         <is>
           <t>This round</t>
         </is>
       </c>
-      <c r="P48" s="26">
+      <c r="C95" s="26">
         <f>Valuation!C10</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="O49" s="26" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="26" t="inlineStr">
         <is>
           <t>Dec 2029</t>
         </is>
       </c>
-      <c r="P49" s="26">
+      <c r="C96" s="26">
         <f>Valuation!D10</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="O50" s="26" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="26" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="P50" s="26">
+      <c r="C97" s="26">
         <f>Valuation!E10</f>
         <v/>
       </c>
-    </row>
-    <row r="51">
-      <c r="O51" s="26" t="n"/>
-      <c r="P51" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/assets/docs/get-lucky-pro-forma.xlsx
+++ b/assets/docs/get-lucky-pro-forma.xlsx
@@ -1597,6 +1597,11 @@
           <t>REVENUE BY STREAM (ZAR)</t>
         </is>
       </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Streams net of third-party shares — the rows add. Peer money in play is a KPI, never revenue.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="n"/>
@@ -1823,6 +1828,11 @@
           <t>PROFITABILITY &amp; CASH (ZAR)</t>
         </is>
       </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Costs budgeted line by line. The cumulative-cash trough is the peak drawdown — inside the R8m raise.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="17" t="n"/>
@@ -2016,6 +2026,11 @@
       <c r="B31" s="16" t="inlineStr">
         <is>
           <t>VALUATION &amp; THE INVESTOR</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Flat 3.0× revenue at every forward milestone, compressing from the 3.69× this round implies.</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2247,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Blue = change me. Black = calculated.</t>
+          <t>Every input in the book, in blue — change any blue cell and the whole workbook restates. The pitch site and dataroom quote this sheet at these values.</t>
         </is>
       </c>
     </row>
@@ -2800,9 +2815,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>Subscribers from ZERO. Milestone is month 36 (Dec 2029).</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>The 72-month engine: subscribers from zero (Jan 2027) → actives → money slips → jackpot entries and peer GMV, month by month. Every other sheet reads from here. Milestone is month 36 (Dec 2029).</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8272,7 @@
     <row r="3">
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Calendar-year totals from the monthly build.</t>
+          <t>Calendar-year totals from the monthly build. Streams are net of third-party shares so the rows add; the memo lines show the insurer's view (gross entries, premium ceded, expected claims).</t>
         </is>
       </c>
     </row>
@@ -9139,6 +9154,11 @@
           <t>TIER LADDER</t>
         </is>
       </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Entry → insured prize, with the mix realised across 10,000 trailing entries. $17.00 weighted entry · $4.08 premium · $1.30 expected claim → 31.9% loss ratio, 2.51× breakeven.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
@@ -9440,7 +9460,14 @@
     <row r="2">
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>VALUATION</t>
+          <t>VALUATION &amp; INVESTOR RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Milestones struck at a flat 3.0× revenue — the round implies 3.69×, so the rating compresses as the company scales. Returns shown on the full R8m for 15%; unrealised marks, not realised returns.</t>
         </is>
       </c>
     </row>
